--- a/summary/no/exposures_meta_analysis_renal_cell_carcinoma_dietary.xlsx
+++ b/summary/no/exposures_meta_analysis_renal_cell_carcinoma_dietary.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Analysis mode" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$K$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$K$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -450,7 +450,7 @@
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
   </cols>
-  <sheetData>
+  <sheetData xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
@@ -509,10 +509,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>green_tea</t>
-        </is>
+      <c r="A2" t="str">
+        <v>green_tea</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
@@ -526,10 +524,10 @@
       <c r="E2" s="3" t="n">
         <v>0.55</v>
       </c>
-      <c r="F2" s="3" t="inlineStr"/>
-      <c r="G2" s="3" t="inlineStr"/>
-      <c r="H2" s="4" t="inlineStr"/>
-      <c r="I2" s="5" t="inlineStr"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="5"/>
       <c r="J2" s="2" t="n">
         <v>549</v>
       </c>
@@ -538,10 +536,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>linoleic_acid</t>
-        </is>
+      <c r="A3" t="str">
+        <v>linoleic_acid</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>1</v>
@@ -555,10 +551,10 @@
       <c r="E3" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="4" t="inlineStr"/>
-      <c r="I3" s="5" t="inlineStr"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="5"/>
       <c r="J3" s="2" t="n">
         <v>2301</v>
       </c>
@@ -567,10 +563,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>tomato</t>
-        </is>
+      <c r="A4" t="str">
+        <v>tomato</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>1</v>
@@ -582,12 +576,12 @@
         <v>0.31</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
+        <v>0.81</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="5"/>
       <c r="J4" s="2" t="n">
         <v>672</v>
       </c>
@@ -596,10 +590,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>quercetin</t>
-        </is>
+      <c r="A5" t="str">
+        <v>quercetin</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>1</v>
@@ -613,10 +605,10 @@
       <c r="E5" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="5"/>
       <c r="J5" s="2" t="n">
         <v>27111</v>
       </c>
@@ -625,10 +617,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>eggs</t>
-        </is>
+      <c r="A6" t="str">
+        <v>eggs</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>1</v>
@@ -642,10 +632,10 @@
       <c r="E6" s="3" t="n">
         <v>0.86</v>
       </c>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="5"/>
       <c r="J6" s="2" t="n">
         <v>1812</v>
       </c>
@@ -654,10 +644,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>vitamin_e</t>
-        </is>
+      <c r="A7" t="str">
+        <v>vitamin_e</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>4</v>
@@ -691,10 +679,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>anti_inflammatory_diet</t>
-        </is>
+      <c r="A8" t="str">
+        <v>anti_inflammatory_diet</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>1</v>
@@ -708,10 +694,10 @@
       <c r="E8" s="3" t="n">
         <v>0.89</v>
       </c>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr"/>
-      <c r="I8" s="5" t="inlineStr"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="5"/>
       <c r="J8" s="2" t="n">
         <v>71421</v>
       </c>
@@ -720,10 +706,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>vitamin_b1</t>
-        </is>
+      <c r="A9" t="str">
+        <v>vitamin_b1</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>2</v>
@@ -737,12 +721,12 @@
       <c r="E9" s="3" t="n">
         <v>0.9196151607361948</v>
       </c>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
       <c r="H9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="5" t="inlineStr"/>
+      <c r="I9" s="5"/>
       <c r="J9" s="2" t="n">
         <v>4597</v>
       </c>
@@ -751,10 +735,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>tea</t>
-        </is>
+      <c r="A10" t="str">
+        <v>tea</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>4</v>
@@ -788,10 +770,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>alcohol</t>
-        </is>
+      <c r="A11" t="str">
+        <v>alcohol</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>20</v>
@@ -825,10 +805,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>vitamin_c</t>
-        </is>
+      <c r="A12" t="str">
+        <v>vitamin_c</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>5</v>
@@ -862,10 +840,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>lutein</t>
-        </is>
+      <c r="A13" t="str">
+        <v>lutein</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>5</v>
@@ -899,10 +875,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>betaine</t>
-        </is>
+      <c r="A14" t="str">
+        <v>betaine</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>1</v>
@@ -916,10 +890,10 @@
       <c r="E14" s="3" t="n">
         <v>1.24</v>
       </c>
-      <c r="F14" s="3" t="inlineStr"/>
-      <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="4" t="inlineStr"/>
-      <c r="I14" s="5" t="inlineStr"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="5"/>
       <c r="J14" s="2" t="n">
         <v>77208</v>
       </c>
@@ -928,10 +902,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>choline</t>
-        </is>
+      <c r="A15" t="str">
+        <v>choline</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>1</v>
@@ -945,10 +917,10 @@
       <c r="E15" s="3" t="n">
         <v>1.27</v>
       </c>
-      <c r="F15" s="3" t="inlineStr"/>
-      <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="4" t="inlineStr"/>
-      <c r="I15" s="5" t="inlineStr"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="5"/>
       <c r="J15" s="2" t="n">
         <v>77208</v>
       </c>
@@ -957,10 +929,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>vitamin_d</t>
-        </is>
+      <c r="A16" t="str">
+        <v>vitamin_d</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>2</v>
@@ -974,12 +944,12 @@
       <c r="E16" s="3" t="n">
         <v>0.9498986350763723</v>
       </c>
-      <c r="F16" s="3" t="inlineStr"/>
-      <c r="G16" s="3" t="inlineStr"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
       <c r="H16" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="5" t="inlineStr"/>
+      <c r="I16" s="5"/>
       <c r="J16" s="2" t="n">
         <v>4112</v>
       </c>
@@ -988,10 +958,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>zeaxanthin</t>
-        </is>
+      <c r="A17" t="str">
+        <v>zeaxanthin</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>2</v>
@@ -1005,12 +973,12 @@
       <c r="E17" s="3" t="n">
         <v>0.9303448082414207</v>
       </c>
-      <c r="F17" s="3" t="inlineStr"/>
-      <c r="G17" s="3" t="inlineStr"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
       <c r="H17" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I17" s="5" t="inlineStr"/>
+      <c r="I17" s="5"/>
       <c r="J17" s="2" t="n">
         <v>781129</v>
       </c>
@@ -1019,10 +987,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>vitamin_b3</t>
-        </is>
+      <c r="A18" t="str">
+        <v>vitamin_b3</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>1</v>
@@ -1036,10 +1002,10 @@
       <c r="E18" s="3" t="n">
         <v>1.07</v>
       </c>
-      <c r="F18" s="3" t="inlineStr"/>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="4" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="5"/>
       <c r="J18" s="2" t="n">
         <v>2301</v>
       </c>
@@ -1048,10 +1014,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>total_dietary_fiber_intake</t>
-        </is>
+      <c r="A19" t="str">
+        <v>total_dietary_fiber_intake</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>2</v>
@@ -1065,12 +1029,12 @@
       <c r="E19" s="3" t="n">
         <v>1.116389703847493</v>
       </c>
-      <c r="F19" s="3" t="inlineStr"/>
-      <c r="G19" s="3" t="inlineStr"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
       <c r="H19" s="4" t="n">
         <v>59.38</v>
       </c>
-      <c r="I19" s="5" t="inlineStr"/>
+      <c r="I19" s="5"/>
       <c r="J19" s="2" t="n">
         <v>4410</v>
       </c>
@@ -1079,10 +1043,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>vitamin_b6</t>
-        </is>
+      <c r="A20" t="str">
+        <v>vitamin_b6</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>1</v>
@@ -1096,10 +1058,10 @@
       <c r="E20" s="3" t="n">
         <v>1.13</v>
       </c>
-      <c r="F20" s="3" t="inlineStr"/>
-      <c r="G20" s="3" t="inlineStr"/>
-      <c r="H20" s="4" t="inlineStr"/>
-      <c r="I20" s="5" t="inlineStr"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="5"/>
       <c r="J20" s="2" t="n">
         <v>2301</v>
       </c>
@@ -1108,10 +1070,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>vitamin_b2</t>
-        </is>
+      <c r="A21" t="str">
+        <v>vitamin_b2</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>1</v>
@@ -1125,10 +1085,10 @@
       <c r="E21" s="3" t="n">
         <v>1.19</v>
       </c>
-      <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="4" t="inlineStr"/>
-      <c r="I21" s="5" t="inlineStr"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="5"/>
       <c r="J21" s="2" t="n">
         <v>2301</v>
       </c>
@@ -1137,10 +1097,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>insoluble_dietary_fiber_intake</t>
-        </is>
+      <c r="A22" t="str">
+        <v>insoluble_dietary_fiber_intake</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>1</v>
@@ -1154,10 +1112,10 @@
       <c r="E22" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="F22" s="3" t="inlineStr"/>
-      <c r="G22" s="3" t="inlineStr"/>
-      <c r="H22" s="4" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="5"/>
       <c r="J22" s="2" t="n">
         <v>2301</v>
       </c>
@@ -1166,10 +1124,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>beta_carotene</t>
-        </is>
+      <c r="A23" t="str">
+        <v>beta_carotene</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>5</v>
@@ -1193,7 +1149,7 @@
         <v>87.95</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>0.7478484537865679</v>
+        <v>0.747848453786568</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>881922</v>
@@ -1203,10 +1159,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>sugar_sweetened_beverage_intake</t>
-        </is>
+      <c r="A24" t="str">
+        <v>sugar_sweetened_beverage_intake</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>1</v>
@@ -1215,15 +1169,15 @@
         <v>0.99</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="E24" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="F24" s="3" t="inlineStr"/>
-      <c r="G24" s="3" t="inlineStr"/>
-      <c r="H24" s="4" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="5"/>
       <c r="J24" s="2" t="n">
         <v>389220</v>
       </c>
@@ -1232,10 +1186,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>lycopene</t>
-        </is>
+      <c r="A25" t="str">
+        <v>lycopene</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>3</v>
@@ -1256,7 +1208,7 @@
         <v>46.47162678478706</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>74.26000000000001</v>
+        <v>74.26</v>
       </c>
       <c r="I25" s="5" t="n">
         <v>0.5668230804465441</v>
@@ -1269,10 +1221,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>animal_protein_intake</t>
-        </is>
+      <c r="A26" t="str">
+        <v>animal_protein_intake</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>1</v>
@@ -1286,10 +1236,10 @@
       <c r="E26" s="3" t="n">
         <v>1.28</v>
       </c>
-      <c r="F26" s="3" t="inlineStr"/>
-      <c r="G26" s="3" t="inlineStr"/>
-      <c r="H26" s="4" t="inlineStr"/>
-      <c r="I26" s="5" t="inlineStr"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="5"/>
       <c r="J26" s="2" t="n">
         <v>774952</v>
       </c>
@@ -1298,10 +1248,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>monounsaturated_fat_mufa</t>
-        </is>
+      <c r="A27" t="str">
+        <v>monounsaturated_fat_mufa</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>1</v>
@@ -1315,10 +1263,10 @@
       <c r="E27" s="3" t="n">
         <v>1.32</v>
       </c>
-      <c r="F27" s="3" t="inlineStr"/>
-      <c r="G27" s="3" t="inlineStr"/>
-      <c r="H27" s="4" t="inlineStr"/>
-      <c r="I27" s="5" t="inlineStr"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="5"/>
       <c r="J27" s="2" t="n">
         <v>774952</v>
       </c>
@@ -1327,10 +1275,8 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>polyunsaturated_fat_pufa</t>
-        </is>
+      <c r="A28" t="str">
+        <v>polyunsaturated_fat_pufa</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>1</v>
@@ -1344,10 +1290,10 @@
       <c r="E28" s="3" t="n">
         <v>1.31</v>
       </c>
-      <c r="F28" s="3" t="inlineStr"/>
-      <c r="G28" s="3" t="inlineStr"/>
-      <c r="H28" s="4" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="5"/>
       <c r="J28" s="2" t="n">
         <v>774952</v>
       </c>
@@ -1356,10 +1302,8 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>processed_meat_intake</t>
-        </is>
+      <c r="A29" t="str">
+        <v>processed_meat_intake</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>6</v>
@@ -1380,7 +1324,7 @@
         <v>2.099663439889117</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>77.01000000000001</v>
+        <v>77.01</v>
       </c>
       <c r="I29" s="5" t="n">
         <v>0.009615835655054888</v>
@@ -1393,10 +1337,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>folic_acid</t>
-        </is>
+      <c r="A30" t="str">
+        <v>folic_acid</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>2</v>
@@ -1410,12 +1352,12 @@
       <c r="E30" s="3" t="n">
         <v>2.321468593851135</v>
       </c>
-      <c r="F30" s="3" t="inlineStr"/>
-      <c r="G30" s="3" t="inlineStr"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
       <c r="H30" s="4" t="n">
-        <v>85.73999999999999</v>
-      </c>
-      <c r="I30" s="5" t="inlineStr"/>
+        <v>85.74</v>
+      </c>
+      <c r="I30" s="5"/>
       <c r="J30" s="2" t="n">
         <v>4597</v>
       </c>
@@ -1424,10 +1366,8 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>calcium</t>
-        </is>
+      <c r="A31" t="str">
+        <v>calcium</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>1</v>
@@ -1441,10 +1381,10 @@
       <c r="E31" s="3" t="n">
         <v>1.58</v>
       </c>
-      <c r="F31" s="3" t="inlineStr"/>
-      <c r="G31" s="3" t="inlineStr"/>
-      <c r="H31" s="4" t="inlineStr"/>
-      <c r="I31" s="5" t="inlineStr"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="5"/>
       <c r="J31" s="2" t="n">
         <v>1811</v>
       </c>
@@ -1453,10 +1393,8 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>vitamin_a</t>
-        </is>
+      <c r="A32" t="str">
+        <v>vitamin_a</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>2</v>
@@ -1470,12 +1408,12 @@
       <c r="E32" s="3" t="n">
         <v>2.865377201601115</v>
       </c>
-      <c r="F32" s="3" t="inlineStr"/>
-      <c r="G32" s="3" t="inlineStr"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
       <c r="H32" s="4" t="n">
         <v>92.64</v>
       </c>
-      <c r="I32" s="5" t="inlineStr"/>
+      <c r="I32" s="5"/>
       <c r="J32" s="2" t="n">
         <v>4597</v>
       </c>
@@ -1484,10 +1422,8 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>potassium</t>
-        </is>
+      <c r="A33" t="str">
+        <v>potassium</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>1</v>
@@ -1501,10 +1437,10 @@
       <c r="E33" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="F33" s="3" t="inlineStr"/>
-      <c r="G33" s="3" t="inlineStr"/>
-      <c r="H33" s="4" t="inlineStr"/>
-      <c r="I33" s="5" t="inlineStr"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="5"/>
       <c r="J33" s="2" t="n">
         <v>120852</v>
       </c>
@@ -1513,10 +1449,8 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>dietary_protein_intake</t>
-        </is>
+      <c r="A34" t="str">
+        <v>dietary_protein_intake</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>2</v>
@@ -1530,12 +1464,12 @@
       <c r="E34" s="3" t="n">
         <v>2.253760151959979</v>
       </c>
-      <c r="F34" s="3" t="inlineStr"/>
-      <c r="G34" s="3" t="inlineStr"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
       <c r="H34" s="4" t="n">
         <v>66.34</v>
       </c>
-      <c r="I34" s="5" t="inlineStr"/>
+      <c r="I34" s="5"/>
       <c r="J34" s="2" t="n">
         <v>776349</v>
       </c>
@@ -1544,10 +1478,8 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>yogurt</t>
-        </is>
+      <c r="A35" t="str">
+        <v>yogurt</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>1</v>
@@ -1561,10 +1493,10 @@
       <c r="E35" s="3" t="n">
         <v>1.67</v>
       </c>
-      <c r="F35" s="3" t="inlineStr"/>
-      <c r="G35" s="3" t="inlineStr"/>
-      <c r="H35" s="4" t="inlineStr"/>
-      <c r="I35" s="5" t="inlineStr"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="5"/>
       <c r="J35" s="2" t="n">
         <v>1812</v>
       </c>
@@ -1573,76 +1505,72 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>red_meat</t>
-        </is>
+      <c r="A36" t="str">
+        <v>ultra_processed_food_intake</v>
       </c>
       <c r="B36" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>1.3752011344215098</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>1.02009932499359</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>1.8541011066724407</v>
+      </c>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="5"/>
+      <c r="J36" s="2" t="n">
+        <v>647537</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>red_meat</v>
+      </c>
+      <c r="B37" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="C37" s="3" t="n">
         <v>1.428035894777088</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>1.125806874101985</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>1.811399951166991</v>
       </c>
-      <c r="F36" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>0.6711000405372343</v>
       </c>
-      <c r="G36" s="3" t="n">
+      <c r="G37" s="3" t="n">
         <v>3.03872208849711</v>
       </c>
-      <c r="H36" s="4" t="n">
+      <c r="H37" s="4" t="n">
         <v>81.58</v>
       </c>
-      <c r="I36" s="5" t="n">
+      <c r="I37" s="5" t="n">
         <v>0.01776300266501832</v>
       </c>
-      <c r="J36" s="2" t="n">
+      <c r="J37" s="2" t="n">
         <v>1768446</v>
       </c>
-      <c r="K36" s="2" t="n">
+      <c r="K37" s="2" t="n">
         <v>5800</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>docosahexaenoic_acid</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" s="3" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="D37" s="3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="F37" s="3" t="inlineStr"/>
-      <c r="G37" s="3" t="inlineStr"/>
-      <c r="H37" s="4" t="inlineStr"/>
-      <c r="I37" s="5" t="inlineStr"/>
-      <c r="J37" s="2" t="n">
-        <v>84063</v>
-      </c>
-      <c r="K37" s="2" t="n">
-        <v>262</v>
-      </c>
-    </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>omega_3_fatty_acids</t>
-        </is>
+      <c r="A38" t="str">
+        <v>docosahexaenoic_acid</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>1</v>
@@ -1654,12 +1582,12 @@
         <v>1.07</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="F38" s="3" t="inlineStr"/>
-      <c r="G38" s="3" t="inlineStr"/>
-      <c r="H38" s="4" t="inlineStr"/>
-      <c r="I38" s="5" t="inlineStr"/>
+        <v>2.27</v>
+      </c>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="5"/>
       <c r="J38" s="2" t="n">
         <v>84063</v>
       </c>
@@ -1668,102 +1596,123 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>oleic_acid</t>
-        </is>
+      <c r="A39" t="str">
+        <v>omega_3_fatty_acids</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C39" s="3" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="2" t="n">
+        <v>84063</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>oleic_acid</v>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="F39" s="3" t="inlineStr"/>
-      <c r="G39" s="3" t="inlineStr"/>
-      <c r="H39" s="4" t="inlineStr"/>
-      <c r="I39" s="5" t="inlineStr"/>
-      <c r="J39" s="2" t="n">
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="2" t="n">
         <v>2143</v>
       </c>
-      <c r="K39" s="2" t="n">
+      <c r="K40" s="2" t="n">
         <v>323</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>selenium</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" s="3" t="n">
+    <row r="41">
+      <c r="A41" t="str">
+        <v>selenium</v>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="F40" s="3" t="inlineStr"/>
-      <c r="G40" s="3" t="inlineStr"/>
-      <c r="H40" s="4" t="inlineStr"/>
-      <c r="I40" s="5" t="inlineStr"/>
-      <c r="J40" s="2" t="n">
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="2" t="n">
         <v>2296</v>
       </c>
-      <c r="K40" s="2" t="n">
+      <c r="K41" s="2" t="n">
         <v>1142</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>dairy</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="n">
+    <row r="42">
+      <c r="A42" t="str">
+        <v>dairy</v>
+      </c>
+      <c r="B42" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="C42" s="3" t="n">
         <v>2.715293362405407</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>1.217987613870554</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>6.052673044477135</v>
       </c>
-      <c r="F41" s="3" t="n">
+      <c r="F42" s="3" t="n">
         <v>0.0003047814843853535</v>
       </c>
-      <c r="G41" s="3" t="n">
+      <c r="G42" s="3" t="n">
         <v>24190.50507215516</v>
       </c>
-      <c r="H41" s="4" t="n">
+      <c r="H42" s="4" t="n">
         <v>73.78</v>
       </c>
-      <c r="I41" s="5" t="n">
+      <c r="I42" s="5" t="n">
         <v>0.1029158875214485</v>
       </c>
-      <c r="J41" s="2" t="n">
+      <c r="J42" s="2" t="n">
         <v>3506</v>
       </c>
-      <c r="K41" s="2" t="n">
+      <c r="K42" s="2" t="n">
         <v>1009</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K41"/>
+  <autoFilter ref="A1:K42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/summary/no/exposures_meta_analysis_renal_cell_carcinoma_dietary.xlsx
+++ b/summary/no/exposures_meta_analysis_renal_cell_carcinoma_dietary.xlsx
@@ -450,7 +450,7 @@
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
   </cols>
-  <sheetData xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
@@ -509,8 +509,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>green_tea</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>green_tea</t>
+        </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
@@ -524,10 +526,10 @@
       <c r="E2" s="3" t="n">
         <v>0.55</v>
       </c>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="5"/>
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr"/>
+      <c r="I2" s="5" t="inlineStr"/>
       <c r="J2" s="2" t="n">
         <v>549</v>
       </c>
@@ -536,8 +538,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>linoleic_acid</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>linoleic_acid</t>
+        </is>
       </c>
       <c r="B3" s="2" t="n">
         <v>1</v>
@@ -551,10 +555,10 @@
       <c r="E3" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="5"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" s="5" t="inlineStr"/>
       <c r="J3" s="2" t="n">
         <v>2301</v>
       </c>
@@ -563,8 +567,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>tomato</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>tomato</t>
+        </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>1</v>
@@ -576,12 +582,12 @@
         <v>0.31</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.81</v>
-      </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="5"/>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
       <c r="J4" s="2" t="n">
         <v>672</v>
       </c>
@@ -590,8 +596,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>quercetin</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>quercetin</t>
+        </is>
       </c>
       <c r="B5" s="2" t="n">
         <v>1</v>
@@ -605,10 +613,10 @@
       <c r="E5" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="5"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" s="5" t="inlineStr"/>
       <c r="J5" s="2" t="n">
         <v>27111</v>
       </c>
@@ -617,8 +625,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v>eggs</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>eggs</t>
+        </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>1</v>
@@ -632,10 +642,10 @@
       <c r="E6" s="3" t="n">
         <v>0.86</v>
       </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="5"/>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
       <c r="J6" s="2" t="n">
         <v>1812</v>
       </c>
@@ -644,8 +654,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
-        <v>vitamin_e</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>vitamin_e</t>
+        </is>
       </c>
       <c r="B7" s="2" t="n">
         <v>4</v>
@@ -679,8 +691,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="str">
-        <v>anti_inflammatory_diet</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>anti_inflammatory_diet</t>
+        </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>1</v>
@@ -694,10 +708,10 @@
       <c r="E8" s="3" t="n">
         <v>0.89</v>
       </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="5"/>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
       <c r="J8" s="2" t="n">
         <v>71421</v>
       </c>
@@ -706,8 +720,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="str">
-        <v>vitamin_b1</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>vitamin_b1</t>
+        </is>
       </c>
       <c r="B9" s="2" t="n">
         <v>2</v>
@@ -721,12 +737,12 @@
       <c r="E9" s="3" t="n">
         <v>0.9196151607361948</v>
       </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="5"/>
+      <c r="I9" s="5" t="inlineStr"/>
       <c r="J9" s="2" t="n">
         <v>4597</v>
       </c>
@@ -735,8 +751,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="str">
-        <v>tea</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tea</t>
+        </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>4</v>
@@ -760,7 +778,7 @@
         <v>77.67</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0.406094525741328</v>
+        <v>0.4060945257413278</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>804643</v>
@@ -770,8 +788,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="str">
-        <v>alcohol</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>alcohol</t>
+        </is>
       </c>
       <c r="B11" s="2" t="n">
         <v>20</v>
@@ -795,7 +815,7 @@
         <v>54.62</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.0025910796269718</v>
+        <v>0.002591079626971808</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>3783725</v>
@@ -805,8 +825,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="str">
-        <v>vitamin_c</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>vitamin_c</t>
+        </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>5</v>
@@ -840,8 +862,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="str">
-        <v>lutein</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>lutein</t>
+        </is>
       </c>
       <c r="B13" s="2" t="n">
         <v>5</v>
@@ -875,8 +899,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="str">
-        <v>betaine</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>betaine</t>
+        </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>1</v>
@@ -890,10 +916,10 @@
       <c r="E14" s="3" t="n">
         <v>1.24</v>
       </c>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="5"/>
+      <c r="F14" s="3" t="inlineStr"/>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr"/>
       <c r="J14" s="2" t="n">
         <v>77208</v>
       </c>
@@ -902,8 +928,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="str">
-        <v>choline</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>choline</t>
+        </is>
       </c>
       <c r="B15" s="2" t="n">
         <v>1</v>
@@ -917,10 +945,10 @@
       <c r="E15" s="3" t="n">
         <v>1.27</v>
       </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="5"/>
+      <c r="F15" s="3" t="inlineStr"/>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr"/>
       <c r="J15" s="2" t="n">
         <v>77208</v>
       </c>
@@ -929,8 +957,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="str">
-        <v>vitamin_d</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>vitamin_d</t>
+        </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>2</v>
@@ -944,12 +974,12 @@
       <c r="E16" s="3" t="n">
         <v>0.9498986350763723</v>
       </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
+      <c r="F16" s="3" t="inlineStr"/>
+      <c r="G16" s="3" t="inlineStr"/>
       <c r="H16" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="5"/>
+      <c r="I16" s="5" t="inlineStr"/>
       <c r="J16" s="2" t="n">
         <v>4112</v>
       </c>
@@ -958,8 +988,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="str">
-        <v>zeaxanthin</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>zeaxanthin</t>
+        </is>
       </c>
       <c r="B17" s="2" t="n">
         <v>2</v>
@@ -973,12 +1005,12 @@
       <c r="E17" s="3" t="n">
         <v>0.9303448082414207</v>
       </c>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
+      <c r="F17" s="3" t="inlineStr"/>
+      <c r="G17" s="3" t="inlineStr"/>
       <c r="H17" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I17" s="5"/>
+      <c r="I17" s="5" t="inlineStr"/>
       <c r="J17" s="2" t="n">
         <v>781129</v>
       </c>
@@ -987,8 +1019,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="str">
-        <v>vitamin_b3</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>vitamin_b3</t>
+        </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>1</v>
@@ -1002,10 +1036,10 @@
       <c r="E18" s="3" t="n">
         <v>1.07</v>
       </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="5"/>
+      <c r="F18" s="3" t="inlineStr"/>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="4" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr"/>
       <c r="J18" s="2" t="n">
         <v>2301</v>
       </c>
@@ -1014,8 +1048,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="str">
-        <v>total_dietary_fiber_intake</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>total_dietary_fiber_intake</t>
+        </is>
       </c>
       <c r="B19" s="2" t="n">
         <v>2</v>
@@ -1029,12 +1065,12 @@
       <c r="E19" s="3" t="n">
         <v>1.116389703847493</v>
       </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
+      <c r="F19" s="3" t="inlineStr"/>
+      <c r="G19" s="3" t="inlineStr"/>
       <c r="H19" s="4" t="n">
         <v>59.38</v>
       </c>
-      <c r="I19" s="5"/>
+      <c r="I19" s="5" t="inlineStr"/>
       <c r="J19" s="2" t="n">
         <v>4410</v>
       </c>
@@ -1043,8 +1079,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="str">
-        <v>vitamin_b6</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>vitamin_b6</t>
+        </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>1</v>
@@ -1058,10 +1096,10 @@
       <c r="E20" s="3" t="n">
         <v>1.13</v>
       </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="5"/>
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="4" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr"/>
       <c r="J20" s="2" t="n">
         <v>2301</v>
       </c>
@@ -1070,8 +1108,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="str">
-        <v>vitamin_b2</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>vitamin_b2</t>
+        </is>
       </c>
       <c r="B21" s="2" t="n">
         <v>1</v>
@@ -1085,10 +1125,10 @@
       <c r="E21" s="3" t="n">
         <v>1.19</v>
       </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="5"/>
+      <c r="F21" s="3" t="inlineStr"/>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr"/>
       <c r="J21" s="2" t="n">
         <v>2301</v>
       </c>
@@ -1097,8 +1137,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="str">
-        <v>insoluble_dietary_fiber_intake</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>insoluble_dietary_fiber_intake</t>
+        </is>
       </c>
       <c r="B22" s="2" t="n">
         <v>1</v>
@@ -1112,10 +1154,10 @@
       <c r="E22" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="5"/>
+      <c r="F22" s="3" t="inlineStr"/>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="4" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
       <c r="J22" s="2" t="n">
         <v>2301</v>
       </c>
@@ -1124,8 +1166,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="str">
-        <v>beta_carotene</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>beta_carotene</t>
+        </is>
       </c>
       <c r="B23" s="2" t="n">
         <v>5</v>
@@ -1149,7 +1193,7 @@
         <v>87.95</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>0.747848453786568</v>
+        <v>0.7478484537865681</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>881922</v>
@@ -1159,8 +1203,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="str">
-        <v>sugar_sweetened_beverage_intake</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>sugar_sweetened_beverage_intake</t>
+        </is>
       </c>
       <c r="B24" s="2" t="n">
         <v>1</v>
@@ -1169,15 +1215,15 @@
         <v>0.99</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>0.94</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E24" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="5"/>
+      <c r="F24" s="3" t="inlineStr"/>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="4" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr"/>
       <c r="J24" s="2" t="n">
         <v>389220</v>
       </c>
@@ -1186,8 +1232,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="str">
-        <v>lycopene</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>lycopene</t>
+        </is>
       </c>
       <c r="B25" s="2" t="n">
         <v>3</v>
@@ -1208,10 +1256,10 @@
         <v>46.47162678478706</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>74.26</v>
+        <v>74.26000000000001</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>0.5668230804465441</v>
+        <v>0.5668230804465442</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>873444</v>
@@ -1221,8 +1269,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="str">
-        <v>animal_protein_intake</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>animal_protein_intake</t>
+        </is>
       </c>
       <c r="B26" s="2" t="n">
         <v>1</v>
@@ -1236,10 +1286,10 @@
       <c r="E26" s="3" t="n">
         <v>1.28</v>
       </c>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="5"/>
+      <c r="F26" s="3" t="inlineStr"/>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="4" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
       <c r="J26" s="2" t="n">
         <v>774952</v>
       </c>
@@ -1248,8 +1298,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="str">
-        <v>monounsaturated_fat_mufa</v>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>monounsaturated_fat_mufa</t>
+        </is>
       </c>
       <c r="B27" s="2" t="n">
         <v>1</v>
@@ -1263,10 +1315,10 @@
       <c r="E27" s="3" t="n">
         <v>1.32</v>
       </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="5"/>
+      <c r="F27" s="3" t="inlineStr"/>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="4" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
       <c r="J27" s="2" t="n">
         <v>774952</v>
       </c>
@@ -1275,8 +1327,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="str">
-        <v>polyunsaturated_fat_pufa</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>polyunsaturated_fat_pufa</t>
+        </is>
       </c>
       <c r="B28" s="2" t="n">
         <v>1</v>
@@ -1290,10 +1344,10 @@
       <c r="E28" s="3" t="n">
         <v>1.31</v>
       </c>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="5"/>
+      <c r="F28" s="3" t="inlineStr"/>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="4" t="inlineStr"/>
+      <c r="I28" s="5" t="inlineStr"/>
       <c r="J28" s="2" t="n">
         <v>774952</v>
       </c>
@@ -1302,8 +1356,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="str">
-        <v>processed_meat_intake</v>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>processed_meat_intake</t>
+        </is>
       </c>
       <c r="B29" s="2" t="n">
         <v>6</v>
@@ -1318,16 +1374,16 @@
         <v>1.410014516884722</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.6286522322</v>
+        <v>0.6286522321999999</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>2.099663439889117</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>77.01</v>
+        <v>77.01000000000001</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>0.009615835655054888</v>
+        <v>0.009615835655054882</v>
       </c>
       <c r="J29" s="2" t="n">
         <v>1766660</v>
@@ -1337,8 +1393,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="str">
-        <v>folic_acid</v>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>folic_acid</t>
+        </is>
       </c>
       <c r="B30" s="2" t="n">
         <v>2</v>
@@ -1352,12 +1410,12 @@
       <c r="E30" s="3" t="n">
         <v>2.321468593851135</v>
       </c>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
+      <c r="F30" s="3" t="inlineStr"/>
+      <c r="G30" s="3" t="inlineStr"/>
       <c r="H30" s="4" t="n">
-        <v>85.74</v>
-      </c>
-      <c r="I30" s="5"/>
+        <v>85.73999999999999</v>
+      </c>
+      <c r="I30" s="5" t="inlineStr"/>
       <c r="J30" s="2" t="n">
         <v>4597</v>
       </c>
@@ -1366,8 +1424,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="str">
-        <v>calcium</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>calcium</t>
+        </is>
       </c>
       <c r="B31" s="2" t="n">
         <v>1</v>
@@ -1381,10 +1441,10 @@
       <c r="E31" s="3" t="n">
         <v>1.58</v>
       </c>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="5"/>
+      <c r="F31" s="3" t="inlineStr"/>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="4" t="inlineStr"/>
+      <c r="I31" s="5" t="inlineStr"/>
       <c r="J31" s="2" t="n">
         <v>1811</v>
       </c>
@@ -1393,8 +1453,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="str">
-        <v>vitamin_a</v>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>vitamin_a</t>
+        </is>
       </c>
       <c r="B32" s="2" t="n">
         <v>2</v>
@@ -1408,12 +1470,12 @@
       <c r="E32" s="3" t="n">
         <v>2.865377201601115</v>
       </c>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
+      <c r="F32" s="3" t="inlineStr"/>
+      <c r="G32" s="3" t="inlineStr"/>
       <c r="H32" s="4" t="n">
         <v>92.64</v>
       </c>
-      <c r="I32" s="5"/>
+      <c r="I32" s="5" t="inlineStr"/>
       <c r="J32" s="2" t="n">
         <v>4597</v>
       </c>
@@ -1422,8 +1484,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="str">
-        <v>potassium</v>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>potassium</t>
+        </is>
       </c>
       <c r="B33" s="2" t="n">
         <v>1</v>
@@ -1437,10 +1501,10 @@
       <c r="E33" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="5"/>
+      <c r="F33" s="3" t="inlineStr"/>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="4" t="inlineStr"/>
+      <c r="I33" s="5" t="inlineStr"/>
       <c r="J33" s="2" t="n">
         <v>120852</v>
       </c>
@@ -1449,8 +1513,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="str">
-        <v>dietary_protein_intake</v>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>dietary_protein_intake</t>
+        </is>
       </c>
       <c r="B34" s="2" t="n">
         <v>2</v>
@@ -1464,12 +1530,12 @@
       <c r="E34" s="3" t="n">
         <v>2.253760151959979</v>
       </c>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
+      <c r="F34" s="3" t="inlineStr"/>
+      <c r="G34" s="3" t="inlineStr"/>
       <c r="H34" s="4" t="n">
         <v>66.34</v>
       </c>
-      <c r="I34" s="5"/>
+      <c r="I34" s="5" t="inlineStr"/>
       <c r="J34" s="2" t="n">
         <v>776349</v>
       </c>
@@ -1478,8 +1544,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="str">
-        <v>yogurt</v>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>yogurt</t>
+        </is>
       </c>
       <c r="B35" s="2" t="n">
         <v>1</v>
@@ -1493,10 +1561,10 @@
       <c r="E35" s="3" t="n">
         <v>1.67</v>
       </c>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="5"/>
+      <c r="F35" s="3" t="inlineStr"/>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="4" t="inlineStr"/>
+      <c r="I35" s="5" t="inlineStr"/>
       <c r="J35" s="2" t="n">
         <v>1812</v>
       </c>
@@ -1505,27 +1573,29 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="str">
-        <v>ultra_processed_food_intake</v>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ultra_processed_food_intake</t>
+        </is>
       </c>
       <c r="B36" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1.3752011344215098</v>
+        <v>1.37520113442151</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>1.02009932499359</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>1.8541011066724407</v>
-      </c>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
+        <v>1.854101106672441</v>
+      </c>
+      <c r="F36" s="3" t="inlineStr"/>
+      <c r="G36" s="3" t="inlineStr"/>
       <c r="H36" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I36" s="5"/>
+      <c r="I36" s="5" t="inlineStr"/>
       <c r="J36" s="2" t="n">
         <v>647537</v>
       </c>
@@ -1534,8 +1604,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="str">
-        <v>red_meat</v>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>red_meat</t>
+        </is>
       </c>
       <c r="B37" s="2" t="n">
         <v>6</v>
@@ -1569,8 +1641,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="str">
-        <v>docosahexaenoic_acid</v>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>docosahexaenoic_acid</t>
+        </is>
       </c>
       <c r="B38" s="2" t="n">
         <v>1</v>
@@ -1584,10 +1658,10 @@
       <c r="E38" s="3" t="n">
         <v>2.27</v>
       </c>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="5"/>
+      <c r="F38" s="3" t="inlineStr"/>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="4" t="inlineStr"/>
+      <c r="I38" s="5" t="inlineStr"/>
       <c r="J38" s="2" t="n">
         <v>84063</v>
       </c>
@@ -1596,8 +1670,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="str">
-        <v>omega_3_fatty_acids</v>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>omega_3_fatty_acids</t>
+        </is>
       </c>
       <c r="B39" s="2" t="n">
         <v>1</v>
@@ -1611,10 +1687,10 @@
       <c r="E39" s="3" t="n">
         <v>2.28</v>
       </c>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="5"/>
+      <c r="F39" s="3" t="inlineStr"/>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="4" t="inlineStr"/>
+      <c r="I39" s="5" t="inlineStr"/>
       <c r="J39" s="2" t="n">
         <v>84063</v>
       </c>
@@ -1623,8 +1699,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="str">
-        <v>oleic_acid</v>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>oleic_acid</t>
+        </is>
       </c>
       <c r="B40" s="2" t="n">
         <v>1</v>
@@ -1638,10 +1716,10 @@
       <c r="E40" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="5"/>
+      <c r="F40" s="3" t="inlineStr"/>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="4" t="inlineStr"/>
+      <c r="I40" s="5" t="inlineStr"/>
       <c r="J40" s="2" t="n">
         <v>2143</v>
       </c>
@@ -1650,8 +1728,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="str">
-        <v>selenium</v>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>selenium</t>
+        </is>
       </c>
       <c r="B41" s="2" t="n">
         <v>1</v>
@@ -1665,10 +1745,10 @@
       <c r="E41" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="5"/>
+      <c r="F41" s="3" t="inlineStr"/>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="4" t="inlineStr"/>
+      <c r="I41" s="5" t="inlineStr"/>
       <c r="J41" s="2" t="n">
         <v>2296</v>
       </c>
@@ -1677,8 +1757,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="str">
-        <v>dairy</v>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
       </c>
       <c r="B42" s="2" t="n">
         <v>3</v>

--- a/summary/no/exposures_meta_analysis_renal_cell_carcinoma_dietary.xlsx
+++ b/summary/no/exposures_meta_analysis_renal_cell_carcinoma_dietary.xlsx
@@ -450,7 +450,7 @@
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
   </cols>
-  <sheetData>
+  <sheetData xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
@@ -509,10 +509,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>green_tea</t>
-        </is>
+      <c r="A2" t="str">
+        <v>green_tea</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
@@ -526,10 +524,10 @@
       <c r="E2" s="3" t="n">
         <v>0.55</v>
       </c>
-      <c r="F2" s="3" t="inlineStr"/>
-      <c r="G2" s="3" t="inlineStr"/>
-      <c r="H2" s="4" t="inlineStr"/>
-      <c r="I2" s="5" t="inlineStr"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="5"/>
       <c r="J2" s="2" t="n">
         <v>549</v>
       </c>
@@ -538,10 +536,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>linoleic_acid</t>
-        </is>
+      <c r="A3" t="str">
+        <v>linoleic_acid</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>1</v>
@@ -555,10 +551,10 @@
       <c r="E3" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="4" t="inlineStr"/>
-      <c r="I3" s="5" t="inlineStr"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="5"/>
       <c r="J3" s="2" t="n">
         <v>2301</v>
       </c>
@@ -567,10 +563,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>tomato</t>
-        </is>
+      <c r="A4" t="str">
+        <v>tomato</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>1</v>
@@ -582,12 +576,12 @@
         <v>0.31</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
+        <v>0.81</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="5"/>
       <c r="J4" s="2" t="n">
         <v>672</v>
       </c>
@@ -596,10 +590,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>quercetin</t>
-        </is>
+      <c r="A5" t="str">
+        <v>quercetin</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>1</v>
@@ -613,10 +605,10 @@
       <c r="E5" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="5"/>
       <c r="J5" s="2" t="n">
         <v>27111</v>
       </c>
@@ -625,10 +617,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>eggs</t>
-        </is>
+      <c r="A6" t="str">
+        <v>eggs</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>1</v>
@@ -642,10 +632,10 @@
       <c r="E6" s="3" t="n">
         <v>0.86</v>
       </c>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="5"/>
       <c r="J6" s="2" t="n">
         <v>1812</v>
       </c>
@@ -654,10 +644,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>vitamin_e</t>
-        </is>
+      <c r="A7" t="str">
+        <v>vitamin_e</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>4</v>
@@ -691,10 +679,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>anti_inflammatory_diet</t>
-        </is>
+      <c r="A8" t="str">
+        <v>anti_inflammatory_diet</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>1</v>
@@ -708,10 +694,10 @@
       <c r="E8" s="3" t="n">
         <v>0.89</v>
       </c>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr"/>
-      <c r="I8" s="5" t="inlineStr"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="5"/>
       <c r="J8" s="2" t="n">
         <v>71421</v>
       </c>
@@ -720,10 +706,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>vitamin_b1</t>
-        </is>
+      <c r="A9" t="str">
+        <v>vitamin_b1</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>2</v>
@@ -737,12 +721,12 @@
       <c r="E9" s="3" t="n">
         <v>0.9196151607361948</v>
       </c>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
       <c r="H9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="5" t="inlineStr"/>
+      <c r="I9" s="5"/>
       <c r="J9" s="2" t="n">
         <v>4597</v>
       </c>
@@ -751,10 +735,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>tea</t>
-        </is>
+      <c r="A10" t="str">
+        <v>tea</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>4</v>
@@ -788,47 +770,43 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>alcohol</t>
-        </is>
+      <c r="A11" t="str">
+        <v>alcohol</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0.7171286688639856</v>
+        <v>0.7166985207200148</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.6528551478261688</v>
+        <v>0.6540967517572572</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0.7877299113272275</v>
+        <v>0.785291729736156</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.5273554843225526</v>
+        <v>0.5315702982473368</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.975193286113776</v>
+        <v>0.9663007344388077</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>54.62</v>
+        <v>52.61</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.002591079626971808</v>
+        <v>0.0019049944016419095</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>3783725</v>
+        <v>3860985</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>11677</v>
+        <v>11926</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>vitamin_c</t>
-        </is>
+      <c r="A12" t="str">
+        <v>vitamin_c</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>5</v>
@@ -862,10 +840,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>lutein</t>
-        </is>
+      <c r="A13" t="str">
+        <v>lutein</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>5</v>
@@ -899,10 +875,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>betaine</t>
-        </is>
+      <c r="A14" t="str">
+        <v>betaine</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>1</v>
@@ -916,10 +890,10 @@
       <c r="E14" s="3" t="n">
         <v>1.24</v>
       </c>
-      <c r="F14" s="3" t="inlineStr"/>
-      <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="4" t="inlineStr"/>
-      <c r="I14" s="5" t="inlineStr"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="5"/>
       <c r="J14" s="2" t="n">
         <v>77208</v>
       </c>
@@ -928,10 +902,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>choline</t>
-        </is>
+      <c r="A15" t="str">
+        <v>choline</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>1</v>
@@ -945,10 +917,10 @@
       <c r="E15" s="3" t="n">
         <v>1.27</v>
       </c>
-      <c r="F15" s="3" t="inlineStr"/>
-      <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="4" t="inlineStr"/>
-      <c r="I15" s="5" t="inlineStr"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="5"/>
       <c r="J15" s="2" t="n">
         <v>77208</v>
       </c>
@@ -957,10 +929,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>vitamin_d</t>
-        </is>
+      <c r="A16" t="str">
+        <v>vitamin_d</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>2</v>
@@ -974,12 +944,12 @@
       <c r="E16" s="3" t="n">
         <v>0.9498986350763723</v>
       </c>
-      <c r="F16" s="3" t="inlineStr"/>
-      <c r="G16" s="3" t="inlineStr"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
       <c r="H16" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="5" t="inlineStr"/>
+      <c r="I16" s="5"/>
       <c r="J16" s="2" t="n">
         <v>4112</v>
       </c>
@@ -988,10 +958,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>zeaxanthin</t>
-        </is>
+      <c r="A17" t="str">
+        <v>zeaxanthin</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>2</v>
@@ -1005,12 +973,12 @@
       <c r="E17" s="3" t="n">
         <v>0.9303448082414207</v>
       </c>
-      <c r="F17" s="3" t="inlineStr"/>
-      <c r="G17" s="3" t="inlineStr"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
       <c r="H17" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I17" s="5" t="inlineStr"/>
+      <c r="I17" s="5"/>
       <c r="J17" s="2" t="n">
         <v>781129</v>
       </c>
@@ -1019,10 +987,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>vitamin_b3</t>
-        </is>
+      <c r="A18" t="str">
+        <v>vitamin_b3</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>1</v>
@@ -1036,10 +1002,10 @@
       <c r="E18" s="3" t="n">
         <v>1.07</v>
       </c>
-      <c r="F18" s="3" t="inlineStr"/>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="4" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="5"/>
       <c r="J18" s="2" t="n">
         <v>2301</v>
       </c>
@@ -1048,10 +1014,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>total_dietary_fiber_intake</t>
-        </is>
+      <c r="A19" t="str">
+        <v>total_dietary_fiber_intake</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>2</v>
@@ -1065,12 +1029,12 @@
       <c r="E19" s="3" t="n">
         <v>1.116389703847493</v>
       </c>
-      <c r="F19" s="3" t="inlineStr"/>
-      <c r="G19" s="3" t="inlineStr"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
       <c r="H19" s="4" t="n">
         <v>59.38</v>
       </c>
-      <c r="I19" s="5" t="inlineStr"/>
+      <c r="I19" s="5"/>
       <c r="J19" s="2" t="n">
         <v>4410</v>
       </c>
@@ -1079,10 +1043,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>vitamin_b6</t>
-        </is>
+      <c r="A20" t="str">
+        <v>vitamin_b6</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>1</v>
@@ -1096,10 +1058,10 @@
       <c r="E20" s="3" t="n">
         <v>1.13</v>
       </c>
-      <c r="F20" s="3" t="inlineStr"/>
-      <c r="G20" s="3" t="inlineStr"/>
-      <c r="H20" s="4" t="inlineStr"/>
-      <c r="I20" s="5" t="inlineStr"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="5"/>
       <c r="J20" s="2" t="n">
         <v>2301</v>
       </c>
@@ -1108,10 +1070,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>vitamin_b2</t>
-        </is>
+      <c r="A21" t="str">
+        <v>vitamin_b2</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>1</v>
@@ -1125,10 +1085,10 @@
       <c r="E21" s="3" t="n">
         <v>1.19</v>
       </c>
-      <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="4" t="inlineStr"/>
-      <c r="I21" s="5" t="inlineStr"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="5"/>
       <c r="J21" s="2" t="n">
         <v>2301</v>
       </c>
@@ -1137,10 +1097,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>insoluble_dietary_fiber_intake</t>
-        </is>
+      <c r="A22" t="str">
+        <v>insoluble_dietary_fiber_intake</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>1</v>
@@ -1154,10 +1112,10 @@
       <c r="E22" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="F22" s="3" t="inlineStr"/>
-      <c r="G22" s="3" t="inlineStr"/>
-      <c r="H22" s="4" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="5"/>
       <c r="J22" s="2" t="n">
         <v>2301</v>
       </c>
@@ -1166,10 +1124,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>beta_carotene</t>
-        </is>
+      <c r="A23" t="str">
+        <v>beta_carotene</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>5</v>
@@ -1203,10 +1159,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>sugar_sweetened_beverage_intake</t>
-        </is>
+      <c r="A24" t="str">
+        <v>sugar_sweetened_beverage_intake</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>1</v>
@@ -1215,15 +1169,15 @@
         <v>0.99</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="E24" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="F24" s="3" t="inlineStr"/>
-      <c r="G24" s="3" t="inlineStr"/>
-      <c r="H24" s="4" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="5"/>
       <c r="J24" s="2" t="n">
         <v>389220</v>
       </c>
@@ -1232,10 +1186,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>lycopene</t>
-        </is>
+      <c r="A25" t="str">
+        <v>lycopene</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>3</v>
@@ -1256,7 +1208,7 @@
         <v>46.47162678478706</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>74.26000000000001</v>
+        <v>74.26</v>
       </c>
       <c r="I25" s="5" t="n">
         <v>0.5668230804465442</v>
@@ -1269,10 +1221,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>animal_protein_intake</t>
-        </is>
+      <c r="A26" t="str">
+        <v>animal_protein_intake</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>1</v>
@@ -1286,10 +1236,10 @@
       <c r="E26" s="3" t="n">
         <v>1.28</v>
       </c>
-      <c r="F26" s="3" t="inlineStr"/>
-      <c r="G26" s="3" t="inlineStr"/>
-      <c r="H26" s="4" t="inlineStr"/>
-      <c r="I26" s="5" t="inlineStr"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="5"/>
       <c r="J26" s="2" t="n">
         <v>774952</v>
       </c>
@@ -1298,10 +1248,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>monounsaturated_fat_mufa</t>
-        </is>
+      <c r="A27" t="str">
+        <v>monounsaturated_fat_mufa</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>1</v>
@@ -1315,10 +1263,10 @@
       <c r="E27" s="3" t="n">
         <v>1.32</v>
       </c>
-      <c r="F27" s="3" t="inlineStr"/>
-      <c r="G27" s="3" t="inlineStr"/>
-      <c r="H27" s="4" t="inlineStr"/>
-      <c r="I27" s="5" t="inlineStr"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="5"/>
       <c r="J27" s="2" t="n">
         <v>774952</v>
       </c>
@@ -1327,10 +1275,8 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>polyunsaturated_fat_pufa</t>
-        </is>
+      <c r="A28" t="str">
+        <v>polyunsaturated_fat_pufa</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>1</v>
@@ -1344,10 +1290,10 @@
       <c r="E28" s="3" t="n">
         <v>1.31</v>
       </c>
-      <c r="F28" s="3" t="inlineStr"/>
-      <c r="G28" s="3" t="inlineStr"/>
-      <c r="H28" s="4" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="5"/>
       <c r="J28" s="2" t="n">
         <v>774952</v>
       </c>
@@ -1356,10 +1302,8 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>processed_meat_intake</t>
-        </is>
+      <c r="A29" t="str">
+        <v>processed_meat_intake</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>6</v>
@@ -1380,7 +1324,7 @@
         <v>2.099663439889117</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>77.01000000000001</v>
+        <v>77.01</v>
       </c>
       <c r="I29" s="5" t="n">
         <v>0.009615835655054882</v>
@@ -1393,10 +1337,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>folic_acid</t>
-        </is>
+      <c r="A30" t="str">
+        <v>folic_acid</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>2</v>
@@ -1410,12 +1352,12 @@
       <c r="E30" s="3" t="n">
         <v>2.321468593851135</v>
       </c>
-      <c r="F30" s="3" t="inlineStr"/>
-      <c r="G30" s="3" t="inlineStr"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
       <c r="H30" s="4" t="n">
-        <v>85.73999999999999</v>
-      </c>
-      <c r="I30" s="5" t="inlineStr"/>
+        <v>85.74</v>
+      </c>
+      <c r="I30" s="5"/>
       <c r="J30" s="2" t="n">
         <v>4597</v>
       </c>
@@ -1424,10 +1366,8 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>calcium</t>
-        </is>
+      <c r="A31" t="str">
+        <v>calcium</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>1</v>
@@ -1441,10 +1381,10 @@
       <c r="E31" s="3" t="n">
         <v>1.58</v>
       </c>
-      <c r="F31" s="3" t="inlineStr"/>
-      <c r="G31" s="3" t="inlineStr"/>
-      <c r="H31" s="4" t="inlineStr"/>
-      <c r="I31" s="5" t="inlineStr"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="5"/>
       <c r="J31" s="2" t="n">
         <v>1811</v>
       </c>
@@ -1453,10 +1393,8 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>vitamin_a</t>
-        </is>
+      <c r="A32" t="str">
+        <v>vitamin_a</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>2</v>
@@ -1470,12 +1408,12 @@
       <c r="E32" s="3" t="n">
         <v>2.865377201601115</v>
       </c>
-      <c r="F32" s="3" t="inlineStr"/>
-      <c r="G32" s="3" t="inlineStr"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
       <c r="H32" s="4" t="n">
         <v>92.64</v>
       </c>
-      <c r="I32" s="5" t="inlineStr"/>
+      <c r="I32" s="5"/>
       <c r="J32" s="2" t="n">
         <v>4597</v>
       </c>
@@ -1484,10 +1422,8 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>potassium</t>
-        </is>
+      <c r="A33" t="str">
+        <v>potassium</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>1</v>
@@ -1501,10 +1437,10 @@
       <c r="E33" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="F33" s="3" t="inlineStr"/>
-      <c r="G33" s="3" t="inlineStr"/>
-      <c r="H33" s="4" t="inlineStr"/>
-      <c r="I33" s="5" t="inlineStr"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="5"/>
       <c r="J33" s="2" t="n">
         <v>120852</v>
       </c>
@@ -1513,10 +1449,8 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>dietary_protein_intake</t>
-        </is>
+      <c r="A34" t="str">
+        <v>dietary_protein_intake</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>2</v>
@@ -1530,12 +1464,12 @@
       <c r="E34" s="3" t="n">
         <v>2.253760151959979</v>
       </c>
-      <c r="F34" s="3" t="inlineStr"/>
-      <c r="G34" s="3" t="inlineStr"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
       <c r="H34" s="4" t="n">
         <v>66.34</v>
       </c>
-      <c r="I34" s="5" t="inlineStr"/>
+      <c r="I34" s="5"/>
       <c r="J34" s="2" t="n">
         <v>776349</v>
       </c>
@@ -1544,10 +1478,8 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>yogurt</t>
-        </is>
+      <c r="A35" t="str">
+        <v>yogurt</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>1</v>
@@ -1561,10 +1493,10 @@
       <c r="E35" s="3" t="n">
         <v>1.67</v>
       </c>
-      <c r="F35" s="3" t="inlineStr"/>
-      <c r="G35" s="3" t="inlineStr"/>
-      <c r="H35" s="4" t="inlineStr"/>
-      <c r="I35" s="5" t="inlineStr"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="5"/>
       <c r="J35" s="2" t="n">
         <v>1812</v>
       </c>
@@ -1573,10 +1505,8 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>ultra_processed_food_intake</t>
-        </is>
+      <c r="A36" t="str">
+        <v>ultra_processed_food_intake</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>2</v>
@@ -1590,12 +1520,12 @@
       <c r="E36" s="3" t="n">
         <v>1.854101106672441</v>
       </c>
-      <c r="F36" s="3" t="inlineStr"/>
-      <c r="G36" s="3" t="inlineStr"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
       <c r="H36" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I36" s="5" t="inlineStr"/>
+      <c r="I36" s="5"/>
       <c r="J36" s="2" t="n">
         <v>647537</v>
       </c>
@@ -1604,10 +1534,8 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>red_meat</t>
-        </is>
+      <c r="A37" t="str">
+        <v>red_meat</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>6</v>
@@ -1641,10 +1569,8 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>docosahexaenoic_acid</t>
-        </is>
+      <c r="A38" t="str">
+        <v>docosahexaenoic_acid</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>1</v>
@@ -1658,10 +1584,10 @@
       <c r="E38" s="3" t="n">
         <v>2.27</v>
       </c>
-      <c r="F38" s="3" t="inlineStr"/>
-      <c r="G38" s="3" t="inlineStr"/>
-      <c r="H38" s="4" t="inlineStr"/>
-      <c r="I38" s="5" t="inlineStr"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="5"/>
       <c r="J38" s="2" t="n">
         <v>84063</v>
       </c>
@@ -1670,10 +1596,8 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>omega_3_fatty_acids</t>
-        </is>
+      <c r="A39" t="str">
+        <v>omega_3_fatty_acids</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>1</v>
@@ -1687,10 +1611,10 @@
       <c r="E39" s="3" t="n">
         <v>2.28</v>
       </c>
-      <c r="F39" s="3" t="inlineStr"/>
-      <c r="G39" s="3" t="inlineStr"/>
-      <c r="H39" s="4" t="inlineStr"/>
-      <c r="I39" s="5" t="inlineStr"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="5"/>
       <c r="J39" s="2" t="n">
         <v>84063</v>
       </c>
@@ -1699,10 +1623,8 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>oleic_acid</t>
-        </is>
+      <c r="A40" t="str">
+        <v>oleic_acid</v>
       </c>
       <c r="B40" s="2" t="n">
         <v>1</v>
@@ -1716,10 +1638,10 @@
       <c r="E40" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="F40" s="3" t="inlineStr"/>
-      <c r="G40" s="3" t="inlineStr"/>
-      <c r="H40" s="4" t="inlineStr"/>
-      <c r="I40" s="5" t="inlineStr"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="5"/>
       <c r="J40" s="2" t="n">
         <v>2143</v>
       </c>
@@ -1728,10 +1650,8 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>selenium</t>
-        </is>
+      <c r="A41" t="str">
+        <v>selenium</v>
       </c>
       <c r="B41" s="2" t="n">
         <v>1</v>
@@ -1745,10 +1665,10 @@
       <c r="E41" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="F41" s="3" t="inlineStr"/>
-      <c r="G41" s="3" t="inlineStr"/>
-      <c r="H41" s="4" t="inlineStr"/>
-      <c r="I41" s="5" t="inlineStr"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="5"/>
       <c r="J41" s="2" t="n">
         <v>2296</v>
       </c>
@@ -1757,10 +1677,8 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>dairy</t>
-        </is>
+      <c r="A42" t="str">
+        <v>dairy</v>
       </c>
       <c r="B42" s="2" t="n">
         <v>3</v>

--- a/summary/no/exposures_meta_analysis_renal_cell_carcinoma_dietary.xlsx
+++ b/summary/no/exposures_meta_analysis_renal_cell_carcinoma_dietary.xlsx
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -49,7 +52,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -57,13 +60,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -450,1264 +462,1346 @@
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
   </cols>
-  <sheetData xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Exposure</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>number estimates</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Pooled RR</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>lower CI RR</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>upper CI RR</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>lower PI RR</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>upper PI RR</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>I^2 (%)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>eggers p-value</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>total N</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>total Cases</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>green_tea</v>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3" t="n">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>green_tea</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="n">
         <v>0.34</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="4" t="n">
         <v>0.21</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="4" t="n">
         <v>0.55</v>
       </c>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="2" t="n">
+      <c r="F2" s="4" t="inlineStr"/>
+      <c r="G2" s="4" t="inlineStr"/>
+      <c r="H2" s="5" t="inlineStr"/>
+      <c r="I2" s="6" t="inlineStr"/>
+      <c r="J2" s="3" t="n">
         <v>549</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="K2" s="3" t="n">
         <v>250</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>linoleic_acid</v>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3" t="n">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>linoleic_acid</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="4" t="n">
         <v>0.4</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="4" t="n">
         <v>0.7</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="2" t="n">
+      <c r="F3" s="4" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr"/>
+      <c r="H3" s="5" t="inlineStr"/>
+      <c r="I3" s="6" t="inlineStr"/>
+      <c r="J3" s="3" t="n">
         <v>2301</v>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="K3" s="3" t="n">
         <v>767</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>tomato</v>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="3" t="n">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>tomato</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="4" t="n">
         <v>0.31</v>
       </c>
-      <c r="E4" s="3" t="n">
-        <v>0.81</v>
-      </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="2" t="n">
+      <c r="E4" s="4" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="3" t="n">
         <v>672</v>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="K4" s="3" t="n">
         <v>335</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>quercetin</v>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="3" t="n">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>quercetin</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="4" t="n">
         <v>0.6</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="4" t="n">
         <v>0.4</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="4" t="n">
         <v>0.9</v>
       </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="2" t="n">
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="5" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="3" t="n">
         <v>27111</v>
       </c>
-      <c r="K5" s="2" t="n">
+      <c r="K5" s="3" t="n">
         <v>228</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v>eggs</v>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="3" t="n">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>eggs</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="4" t="n">
         <v>0.64</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="4" t="n">
         <v>0.48</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="4" t="n">
         <v>0.86</v>
       </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="2" t="n">
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="3" t="n">
         <v>1812</v>
       </c>
-      <c r="K6" s="2" t="n">
+      <c r="K6" s="3" t="n">
         <v>777</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
-        <v>vitamin_e</v>
-      </c>
-      <c r="B7" s="2" t="n">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>vitamin_e</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C7" s="4" t="n">
         <v>0.6704541234521412</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="4" t="n">
         <v>0.4526663314814308</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="4" t="n">
         <v>0.9929251454538985</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>0.1198875658458504</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>3.749419120177572</v>
-      </c>
-      <c r="H7" s="4" t="n">
+      <c r="F7" s="4" t="n">
+        <v>0.1198875658484078</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>3.749419120097587</v>
+      </c>
+      <c r="H7" s="5" t="n">
         <v>75.61</v>
       </c>
-      <c r="I7" s="5" t="n">
-        <v>0.5015932102841117</v>
-      </c>
-      <c r="J7" s="2" t="n">
+      <c r="I7" s="6" t="n">
+        <v>0.5015932102841116</v>
+      </c>
+      <c r="J7" s="3" t="n">
         <v>127855</v>
       </c>
-      <c r="K7" s="2" t="n">
+      <c r="K7" s="3" t="n">
         <v>2404</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="str">
-        <v>anti_inflammatory_diet</v>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="3" t="n">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>anti_inflammatory_diet</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="4" t="n">
         <v>0.68</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="4" t="n">
         <v>0.52</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="4" t="n">
         <v>0.89</v>
       </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="2" t="n">
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="3" t="n">
         <v>71421</v>
       </c>
-      <c r="K8" s="2" t="n">
+      <c r="K8" s="3" t="n">
         <v>431</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="str">
-        <v>vitamin_b1</v>
-      </c>
-      <c r="B9" s="2" t="n">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>vitamin_b1</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="C9" s="4" t="n">
         <v>0.7116279829325146</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="4" t="n">
         <v>0.5506807713861427</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="4" t="n">
         <v>0.9196151607361948</v>
       </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="4" t="n">
+      <c r="F9" s="4" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="5"/>
-      <c r="J9" s="2" t="n">
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="3" t="n">
         <v>4597</v>
       </c>
-      <c r="K9" s="2" t="n">
+      <c r="K9" s="3" t="n">
         <v>1909</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="str">
-        <v>tea</v>
-      </c>
-      <c r="B10" s="2" t="n">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tea</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="C10" s="4" t="n">
         <v>0.7142658835761514</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" s="4" t="n">
         <v>0.5123229966574786</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" s="4" t="n">
         <v>0.9958088076649545</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>0.1670242223297662</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>3.054501588599221</v>
-      </c>
-      <c r="H10" s="4" t="n">
+      <c r="F10" s="4" t="n">
+        <v>0.1670242223327739</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>3.054501588544217</v>
+      </c>
+      <c r="H10" s="5" t="n">
         <v>77.67</v>
       </c>
-      <c r="I10" s="5" t="n">
-        <v>0.4060945257413278</v>
-      </c>
-      <c r="J10" s="2" t="n">
+      <c r="I10" s="6" t="n">
+        <v>0.4060945257413281</v>
+      </c>
+      <c r="J10" s="3" t="n">
         <v>804643</v>
       </c>
-      <c r="K10" s="2" t="n">
+      <c r="K10" s="3" t="n">
         <v>2861</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="str">
-        <v>alcohol</v>
-      </c>
-      <c r="B11" s="2" t="n">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>alcohol</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="C11" s="4" t="n">
         <v>0.7166985207200148</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" s="4" t="n">
         <v>0.6540967517572572</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" s="4" t="n">
         <v>0.785291729736156</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>0.5315702982473368</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>0.9663007344388077</v>
-      </c>
-      <c r="H11" s="4" t="n">
+      <c r="F11" s="4" t="n">
+        <v>0.5315702982473401</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>0.9663007344388015</v>
+      </c>
+      <c r="H11" s="5" t="n">
         <v>52.61</v>
       </c>
-      <c r="I11" s="5" t="n">
-        <v>0.0019049944016419095</v>
-      </c>
-      <c r="J11" s="2" t="n">
+      <c r="I11" s="6" t="n">
+        <v>0.00190499440164191</v>
+      </c>
+      <c r="J11" s="3" t="n">
         <v>3860985</v>
       </c>
-      <c r="K11" s="2" t="n">
+      <c r="K11" s="3" t="n">
         <v>11926</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="str">
-        <v>vitamin_c</v>
-      </c>
-      <c r="B12" s="2" t="n">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>vitamin_c</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="C12" s="4" t="n">
         <v>0.7585094662858782</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" s="4" t="n">
         <v>0.6137301147444475</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="E12" s="4" t="n">
         <v>0.9374423653381478</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>0.4223806276719194</v>
-      </c>
-      <c r="G12" s="3" t="n">
-        <v>1.362128309758031</v>
-      </c>
-      <c r="H12" s="4" t="n">
+      <c r="F12" s="4" t="n">
+        <v>0.4223806276718763</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>1.36212830975817</v>
+      </c>
+      <c r="H12" s="5" t="n">
         <v>39.11</v>
       </c>
-      <c r="I12" s="5" t="n">
-        <v>0.2965256086013334</v>
-      </c>
-      <c r="J12" s="2" t="n">
+      <c r="I12" s="6" t="n">
+        <v>0.2965256086013331</v>
+      </c>
+      <c r="J12" s="3" t="n">
         <v>128222</v>
       </c>
-      <c r="K12" s="2" t="n">
+      <c r="K12" s="3" t="n">
         <v>2559</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="str">
-        <v>lutein</v>
-      </c>
-      <c r="B13" s="2" t="n">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>lutein</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="C13" s="4" t="n">
         <v>0.7710515858035663</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="4" t="n">
         <v>0.6804506362045877</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="E13" s="4" t="n">
         <v>0.8737159116880344</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>0.6293674105587818</v>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>0.9446319240495011</v>
-      </c>
-      <c r="H13" s="4" t="n">
+      <c r="F13" s="4" t="n">
+        <v>0.6293674105587594</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>0.9446319240495346</v>
+      </c>
+      <c r="H13" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="5" t="n">
-        <v>0.5547361243986885</v>
-      </c>
-      <c r="J13" s="2" t="n">
+      <c r="I13" s="6" t="n">
+        <v>0.5547361243986886</v>
+      </c>
+      <c r="J13" s="3" t="n">
         <v>881922</v>
       </c>
-      <c r="K13" s="2" t="n">
+      <c r="K13" s="3" t="n">
         <v>4765</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="str">
-        <v>betaine</v>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="3" t="n">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>betaine</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="4" t="n">
         <v>0.78</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" s="4" t="n">
         <v>0.49</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" s="4" t="n">
         <v>1.24</v>
       </c>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="2" t="n">
+      <c r="F14" s="4" t="inlineStr"/>
+      <c r="G14" s="4" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="6" t="inlineStr"/>
+      <c r="J14" s="3" t="n">
         <v>77208</v>
       </c>
-      <c r="K14" s="2" t="n">
+      <c r="K14" s="3" t="n">
         <v>225</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="str">
-        <v>choline</v>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="3" t="n">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>choline</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="4" t="n">
         <v>0.78</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="D15" s="4" t="n">
         <v>0.48</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="E15" s="4" t="n">
         <v>1.27</v>
       </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="2" t="n">
+      <c r="F15" s="4" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr"/>
+      <c r="I15" s="6" t="inlineStr"/>
+      <c r="J15" s="3" t="n">
         <v>77208</v>
       </c>
-      <c r="K15" s="2" t="n">
+      <c r="K15" s="3" t="n">
         <v>225</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="str">
-        <v>vitamin_d</v>
-      </c>
-      <c r="B16" s="2" t="n">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>vitamin_d</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="C16" s="4" t="n">
         <v>0.7883603473970939</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D16" s="4" t="n">
         <v>0.6542930102200819</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="E16" s="4" t="n">
         <v>0.9498986350763723</v>
       </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="4" t="n">
+      <c r="F16" s="4" t="inlineStr"/>
+      <c r="G16" s="4" t="inlineStr"/>
+      <c r="H16" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="5"/>
-      <c r="J16" s="2" t="n">
+      <c r="I16" s="6" t="inlineStr"/>
+      <c r="J16" s="3" t="n">
         <v>4112</v>
       </c>
-      <c r="K16" s="2" t="n">
+      <c r="K16" s="3" t="n">
         <v>767</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="str">
-        <v>zeaxanthin</v>
-      </c>
-      <c r="B17" s="2" t="n">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>zeaxanthin</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="C17" s="4" t="n">
         <v>0.7904917964964951</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="D17" s="4" t="n">
         <v>0.6716620276620098</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="E17" s="4" t="n">
         <v>0.9303448082414207</v>
       </c>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="4" t="n">
+      <c r="F17" s="4" t="inlineStr"/>
+      <c r="G17" s="4" t="inlineStr"/>
+      <c r="H17" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I17" s="5"/>
-      <c r="J17" s="2" t="n">
+      <c r="I17" s="6" t="inlineStr"/>
+      <c r="J17" s="3" t="n">
         <v>781129</v>
       </c>
-      <c r="K17" s="2" t="n">
+      <c r="K17" s="3" t="n">
         <v>2616</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="str">
-        <v>vitamin_b3</v>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" s="3" t="n">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>vitamin_b3</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="4" t="n">
         <v>0.8</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D18" s="4" t="n">
         <v>0.6</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="E18" s="4" t="n">
         <v>1.07</v>
       </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="2" t="n">
+      <c r="F18" s="4" t="inlineStr"/>
+      <c r="G18" s="4" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="6" t="inlineStr"/>
+      <c r="J18" s="3" t="n">
         <v>2301</v>
       </c>
-      <c r="K18" s="2" t="n">
+      <c r="K18" s="3" t="n">
         <v>767</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="str">
-        <v>total_dietary_fiber_intake</v>
-      </c>
-      <c r="B19" s="2" t="n">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>total_dietary_fiber_intake</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="C19" s="4" t="n">
         <v>0.8469615338010708</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="D19" s="4" t="n">
         <v>0.6424925870144645</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="E19" s="4" t="n">
         <v>1.116389703847493</v>
       </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="4" t="n">
+      <c r="F19" s="4" t="inlineStr"/>
+      <c r="G19" s="4" t="inlineStr"/>
+      <c r="H19" s="5" t="n">
         <v>59.38</v>
       </c>
-      <c r="I19" s="5"/>
-      <c r="J19" s="2" t="n">
+      <c r="I19" s="6" t="inlineStr"/>
+      <c r="J19" s="3" t="n">
         <v>4410</v>
       </c>
-      <c r="K19" s="2" t="n">
+      <c r="K19" s="3" t="n">
         <v>1621</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="str">
-        <v>vitamin_b6</v>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" s="3" t="n">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>vitamin_b6</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="4" t="n">
         <v>0.85</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="D20" s="4" t="n">
         <v>0.64</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="E20" s="4" t="n">
         <v>1.13</v>
       </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="2" t="n">
+      <c r="F20" s="4" t="inlineStr"/>
+      <c r="G20" s="4" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="6" t="inlineStr"/>
+      <c r="J20" s="3" t="n">
         <v>2301</v>
       </c>
-      <c r="K20" s="2" t="n">
+      <c r="K20" s="3" t="n">
         <v>767</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="str">
-        <v>vitamin_b2</v>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" s="3" t="n">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>vitamin_b2</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="4" t="n">
         <v>0.88</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="D21" s="4" t="n">
         <v>0.66</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="E21" s="4" t="n">
         <v>1.19</v>
       </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="2" t="n">
+      <c r="F21" s="4" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr"/>
+      <c r="I21" s="6" t="inlineStr"/>
+      <c r="J21" s="3" t="n">
         <v>2301</v>
       </c>
-      <c r="K21" s="2" t="n">
+      <c r="K21" s="3" t="n">
         <v>767</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="str">
-        <v>insoluble_dietary_fiber_intake</v>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" s="3" t="n">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>insoluble_dietary_fiber_intake</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="4" t="n">
         <v>0.92</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="D22" s="4" t="n">
         <v>0.8</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="E22" s="4" t="n">
         <v>1.05</v>
       </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="2" t="n">
+      <c r="F22" s="4" t="inlineStr"/>
+      <c r="G22" s="4" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="6" t="inlineStr"/>
+      <c r="J22" s="3" t="n">
         <v>2301</v>
       </c>
-      <c r="K22" s="2" t="n">
+      <c r="K22" s="3" t="n">
         <v>767</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="str">
-        <v>beta_carotene</v>
-      </c>
-      <c r="B23" s="2" t="n">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>beta_carotene</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="C23" s="4" t="n">
         <v>0.9776534669582103</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="D23" s="4" t="n">
         <v>0.7008229441190426</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="E23" s="4" t="n">
         <v>1.363697826425325</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>0.2848991490981571</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>3.354893492946523</v>
-      </c>
-      <c r="H23" s="4" t="n">
+      <c r="F23" s="4" t="n">
+        <v>0.2848991490980958</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>3.354893492947245</v>
+      </c>
+      <c r="H23" s="5" t="n">
         <v>87.95</v>
       </c>
-      <c r="I23" s="5" t="n">
-        <v>0.7478484537865681</v>
-      </c>
-      <c r="J23" s="2" t="n">
+      <c r="I23" s="6" t="n">
+        <v>0.7478484537865678</v>
+      </c>
+      <c r="J23" s="3" t="n">
         <v>881922</v>
       </c>
-      <c r="K23" s="2" t="n">
+      <c r="K23" s="3" t="n">
         <v>4765</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="str">
-        <v>sugar_sweetened_beverage_intake</v>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" s="3" t="n">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>sugar_sweetened_beverage_intake</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="4" t="n">
         <v>0.99</v>
       </c>
-      <c r="D24" s="3" t="n">
-        <v>0.94</v>
-      </c>
-      <c r="E24" s="3" t="n">
+      <c r="D24" s="4" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E24" s="4" t="n">
         <v>1.05</v>
       </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="5"/>
-      <c r="J24" s="2" t="n">
+      <c r="F24" s="4" t="inlineStr"/>
+      <c r="G24" s="4" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="6" t="inlineStr"/>
+      <c r="J24" s="3" t="n">
         <v>389220</v>
       </c>
-      <c r="K24" s="2" t="n">
+      <c r="K24" s="3" t="n">
         <v>888</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="str">
-        <v>lycopene</v>
-      </c>
-      <c r="B25" s="2" t="n">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>lycopene</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="C25" s="4" t="n">
         <v>1.017450511698055</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="D25" s="4" t="n">
         <v>0.7301538599450065</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="E25" s="4" t="n">
         <v>1.417790962349503</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>0.0222760771545342</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>46.47162678478706</v>
-      </c>
-      <c r="H25" s="4" t="n">
-        <v>74.26</v>
-      </c>
-      <c r="I25" s="5" t="n">
-        <v>0.5668230804465442</v>
-      </c>
-      <c r="J25" s="2" t="n">
+      <c r="F25" s="4" t="n">
+        <v>0.02227607715280967</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>46.47162678838473</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>74.26000000000001</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>0.5668230804465443</v>
+      </c>
+      <c r="J25" s="3" t="n">
         <v>873444</v>
       </c>
-      <c r="K25" s="2" t="n">
+      <c r="K25" s="3" t="n">
         <v>2860</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="str">
-        <v>animal_protein_intake</v>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="3" t="n">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>animal_protein_intake</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="4" t="n">
         <v>1.05</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="D26" s="4" t="n">
         <v>0.85</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="E26" s="4" t="n">
         <v>1.28</v>
       </c>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="5"/>
-      <c r="J26" s="2" t="n">
+      <c r="F26" s="4" t="inlineStr"/>
+      <c r="G26" s="4" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="6" t="inlineStr"/>
+      <c r="J26" s="3" t="n">
         <v>774952</v>
       </c>
-      <c r="K26" s="2" t="n">
+      <c r="K26" s="3" t="n">
         <v>1019</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="str">
-        <v>monounsaturated_fat_mufa</v>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" s="3" t="n">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>monounsaturated_fat_mufa</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="4" t="n">
         <v>1.1</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="D27" s="4" t="n">
         <v>0.92</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="E27" s="4" t="n">
         <v>1.32</v>
       </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="5"/>
-      <c r="J27" s="2" t="n">
+      <c r="F27" s="4" t="inlineStr"/>
+      <c r="G27" s="4" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr"/>
+      <c r="I27" s="6" t="inlineStr"/>
+      <c r="J27" s="3" t="n">
         <v>774952</v>
       </c>
-      <c r="K27" s="2" t="n">
+      <c r="K27" s="3" t="n">
         <v>1478</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="str">
-        <v>polyunsaturated_fat_pufa</v>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" s="3" t="n">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>polyunsaturated_fat_pufa</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="4" t="n">
         <v>1.1</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="D28" s="4" t="n">
         <v>0.93</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="E28" s="4" t="n">
         <v>1.31</v>
       </c>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="5"/>
-      <c r="J28" s="2" t="n">
+      <c r="F28" s="4" t="inlineStr"/>
+      <c r="G28" s="4" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr"/>
+      <c r="I28" s="6" t="inlineStr"/>
+      <c r="J28" s="3" t="n">
         <v>774952</v>
       </c>
-      <c r="K28" s="2" t="n">
+      <c r="K28" s="3" t="n">
         <v>1478</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="str">
-        <v>processed_meat_intake</v>
-      </c>
-      <c r="B29" s="2" t="n">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>processed_meat_intake</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="C29" s="4" t="n">
         <v>1.148894298164554</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="D29" s="4" t="n">
         <v>0.9362244820588583</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="E29" s="4" t="n">
         <v>1.410014516884722</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>0.6286522321999999</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>2.099663439889117</v>
-      </c>
-      <c r="H29" s="4" t="n">
-        <v>77.01</v>
-      </c>
-      <c r="I29" s="5" t="n">
-        <v>0.009615835655054882</v>
-      </c>
-      <c r="J29" s="2" t="n">
+      <c r="F29" s="4" t="n">
+        <v>0.6286522321999992</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>2.099663439889119</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>77.01000000000001</v>
+      </c>
+      <c r="I29" s="6" t="n">
+        <v>0.009615835655054888</v>
+      </c>
+      <c r="J29" s="3" t="n">
         <v>1766660</v>
       </c>
-      <c r="K29" s="2" t="n">
+      <c r="K29" s="3" t="n">
         <v>5212</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="str">
-        <v>folic_acid</v>
-      </c>
-      <c r="B30" s="2" t="n">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>folic_acid</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="C30" s="4" t="n">
         <v>1.178214315092722</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="D30" s="4" t="n">
         <v>0.5980385872137474</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="E30" s="4" t="n">
         <v>2.321468593851135</v>
       </c>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="4" t="n">
-        <v>85.74</v>
-      </c>
-      <c r="I30" s="5"/>
-      <c r="J30" s="2" t="n">
+      <c r="F30" s="4" t="inlineStr"/>
+      <c r="G30" s="4" t="inlineStr"/>
+      <c r="H30" s="5" t="n">
+        <v>85.73999999999999</v>
+      </c>
+      <c r="I30" s="6" t="inlineStr"/>
+      <c r="J30" s="3" t="n">
         <v>4597</v>
       </c>
-      <c r="K30" s="2" t="n">
+      <c r="K30" s="3" t="n">
         <v>1909</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="str">
-        <v>calcium</v>
-      </c>
-      <c r="B31" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C31" s="3" t="n">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>calcium</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" s="4" t="n">
         <v>1.2</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="D31" s="4" t="n">
         <v>0.92</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="E31" s="4" t="n">
         <v>1.58</v>
       </c>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="5"/>
-      <c r="J31" s="2" t="n">
+      <c r="F31" s="4" t="inlineStr"/>
+      <c r="G31" s="4" t="inlineStr"/>
+      <c r="H31" s="5" t="inlineStr"/>
+      <c r="I31" s="6" t="inlineStr"/>
+      <c r="J31" s="3" t="n">
         <v>1811</v>
       </c>
-      <c r="K31" s="2" t="n">
+      <c r="K31" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="str">
-        <v>vitamin_a</v>
-      </c>
-      <c r="B32" s="2" t="n">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>vitamin_a</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="C32" s="4" t="n">
         <v>1.227525064963178</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="D32" s="4" t="n">
         <v>0.5259232444453181</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="E32" s="4" t="n">
         <v>2.865377201601115</v>
       </c>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="4" t="n">
+      <c r="F32" s="4" t="inlineStr"/>
+      <c r="G32" s="4" t="inlineStr"/>
+      <c r="H32" s="5" t="n">
         <v>92.64</v>
       </c>
-      <c r="I32" s="5"/>
-      <c r="J32" s="2" t="n">
+      <c r="I32" s="6" t="inlineStr"/>
+      <c r="J32" s="3" t="n">
         <v>4597</v>
       </c>
-      <c r="K32" s="2" t="n">
+      <c r="K32" s="3" t="n">
         <v>1909</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="str">
-        <v>potassium</v>
-      </c>
-      <c r="B33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" s="3" t="n">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>potassium</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" s="4" t="n">
         <v>1.28</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="D33" s="4" t="n">
         <v>0.87</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="E33" s="4" t="n">
         <v>1.9</v>
       </c>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="5"/>
-      <c r="J33" s="2" t="n">
+      <c r="F33" s="4" t="inlineStr"/>
+      <c r="G33" s="4" t="inlineStr"/>
+      <c r="H33" s="5" t="inlineStr"/>
+      <c r="I33" s="6" t="inlineStr"/>
+      <c r="J33" s="3" t="n">
         <v>120852</v>
       </c>
-      <c r="K33" s="2" t="n">
+      <c r="K33" s="3" t="n">
         <v>485</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="str">
-        <v>dietary_protein_intake</v>
-      </c>
-      <c r="B34" s="2" t="n">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>dietary_protein_intake</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="C34" s="4" t="n">
         <v>1.303822063731362</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="D34" s="4" t="n">
         <v>0.7543491156730364</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="E34" s="4" t="n">
         <v>2.253760151959979</v>
       </c>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="4" t="n">
+      <c r="F34" s="4" t="inlineStr"/>
+      <c r="G34" s="4" t="inlineStr"/>
+      <c r="H34" s="5" t="n">
         <v>66.34</v>
       </c>
-      <c r="I34" s="5"/>
-      <c r="J34" s="2" t="n">
+      <c r="I34" s="6" t="inlineStr"/>
+      <c r="J34" s="3" t="n">
         <v>776349</v>
       </c>
-      <c r="K34" s="2" t="n">
+      <c r="K34" s="3" t="n">
         <v>2168</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="str">
-        <v>yogurt</v>
-      </c>
-      <c r="B35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" s="3" t="n">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>yogurt</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="4" t="n">
         <v>1.31</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="D35" s="4" t="n">
         <v>1.03</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="E35" s="4" t="n">
         <v>1.67</v>
       </c>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="5"/>
-      <c r="J35" s="2" t="n">
+      <c r="F35" s="4" t="inlineStr"/>
+      <c r="G35" s="4" t="inlineStr"/>
+      <c r="H35" s="5" t="inlineStr"/>
+      <c r="I35" s="6" t="inlineStr"/>
+      <c r="J35" s="3" t="n">
         <v>1812</v>
       </c>
-      <c r="K35" s="2" t="n">
+      <c r="K35" s="3" t="n">
         <v>777</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="str">
-        <v>ultra_processed_food_intake</v>
-      </c>
-      <c r="B36" s="2" t="n">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ultra_processed_food_intake</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="C36" s="4" t="n">
         <v>1.37520113442151</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="D36" s="4" t="n">
         <v>1.02009932499359</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="E36" s="4" t="n">
         <v>1.854101106672441</v>
       </c>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="4" t="n">
+      <c r="F36" s="4" t="inlineStr"/>
+      <c r="G36" s="4" t="inlineStr"/>
+      <c r="H36" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I36" s="5"/>
-      <c r="J36" s="2" t="n">
+      <c r="I36" s="6" t="inlineStr"/>
+      <c r="J36" s="3" t="n">
         <v>647537</v>
       </c>
-      <c r="K36" s="2" t="n">
+      <c r="K36" s="3" t="n">
         <v>594</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="str">
-        <v>red_meat</v>
-      </c>
-      <c r="B37" s="2" t="n">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>red_meat</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="C37" s="4" t="n">
         <v>1.428035894777088</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="D37" s="4" t="n">
         <v>1.125806874101985</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="E37" s="4" t="n">
         <v>1.811399951166991</v>
       </c>
-      <c r="F37" s="3" t="n">
-        <v>0.6711000405372343</v>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>3.03872208849711</v>
-      </c>
-      <c r="H37" s="4" t="n">
+      <c r="F37" s="4" t="n">
+        <v>0.6711000405372333</v>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>3.038722088497114</v>
+      </c>
+      <c r="H37" s="5" t="n">
         <v>81.58</v>
       </c>
-      <c r="I37" s="5" t="n">
-        <v>0.01776300266501832</v>
-      </c>
-      <c r="J37" s="2" t="n">
+      <c r="I37" s="6" t="n">
+        <v>0.01776300266501834</v>
+      </c>
+      <c r="J37" s="3" t="n">
         <v>1768446</v>
       </c>
-      <c r="K37" s="2" t="n">
+      <c r="K37" s="3" t="n">
         <v>5800</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="str">
-        <v>docosahexaenoic_acid</v>
-      </c>
-      <c r="B38" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" s="3" t="n">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>docosahexaenoic_acid</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" s="4" t="n">
         <v>1.56</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="D38" s="4" t="n">
         <v>1.07</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="E38" s="4" t="n">
         <v>2.27</v>
       </c>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="5"/>
-      <c r="J38" s="2" t="n">
+      <c r="F38" s="4" t="inlineStr"/>
+      <c r="G38" s="4" t="inlineStr"/>
+      <c r="H38" s="5" t="inlineStr"/>
+      <c r="I38" s="6" t="inlineStr"/>
+      <c r="J38" s="3" t="n">
         <v>84063</v>
       </c>
-      <c r="K38" s="2" t="n">
+      <c r="K38" s="3" t="n">
         <v>262</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="str">
-        <v>omega_3_fatty_acids</v>
-      </c>
-      <c r="B39" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C39" s="3" t="n">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>omega_3_fatty_acids</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" s="4" t="n">
         <v>1.56</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="D39" s="4" t="n">
         <v>1.07</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="E39" s="4" t="n">
         <v>2.28</v>
       </c>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="5"/>
-      <c r="J39" s="2" t="n">
+      <c r="F39" s="4" t="inlineStr"/>
+      <c r="G39" s="4" t="inlineStr"/>
+      <c r="H39" s="5" t="inlineStr"/>
+      <c r="I39" s="6" t="inlineStr"/>
+      <c r="J39" s="3" t="n">
         <v>84063</v>
       </c>
-      <c r="K39" s="2" t="n">
+      <c r="K39" s="3" t="n">
         <v>262</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="str">
-        <v>oleic_acid</v>
-      </c>
-      <c r="B40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" s="3" t="n">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>oleic_acid</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="4" t="n">
         <v>1.9</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="D40" s="4" t="n">
         <v>1.2</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="E40" s="4" t="n">
         <v>2.9</v>
       </c>
-      <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="5"/>
-      <c r="J40" s="2" t="n">
+      <c r="F40" s="4" t="inlineStr"/>
+      <c r="G40" s="4" t="inlineStr"/>
+      <c r="H40" s="5" t="inlineStr"/>
+      <c r="I40" s="6" t="inlineStr"/>
+      <c r="J40" s="3" t="n">
         <v>2143</v>
       </c>
-      <c r="K40" s="2" t="n">
+      <c r="K40" s="3" t="n">
         <v>323</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="str">
-        <v>selenium</v>
-      </c>
-      <c r="B41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C41" s="3" t="n">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>selenium</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="D41" s="4" t="n">
         <v>1.3</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="E41" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="5"/>
-      <c r="J41" s="2" t="n">
+      <c r="F41" s="4" t="inlineStr"/>
+      <c r="G41" s="4" t="inlineStr"/>
+      <c r="H41" s="5" t="inlineStr"/>
+      <c r="I41" s="6" t="inlineStr"/>
+      <c r="J41" s="3" t="n">
         <v>2296</v>
       </c>
-      <c r="K41" s="2" t="n">
+      <c r="K41" s="3" t="n">
         <v>1142</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="str">
-        <v>dairy</v>
-      </c>
-      <c r="B42" s="2" t="n">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="C42" s="4" t="n">
         <v>2.715293362405407</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="D42" s="4" t="n">
         <v>1.217987613870554</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="E42" s="4" t="n">
         <v>6.052673044477135</v>
       </c>
-      <c r="F42" s="3" t="n">
-        <v>0.0003047814843853535</v>
-      </c>
-      <c r="G42" s="3" t="n">
-        <v>24190.50507215516</v>
-      </c>
-      <c r="H42" s="4" t="n">
+      <c r="F42" s="4" t="n">
+        <v>0.0003047814843291999</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>24190.50507661207</v>
+      </c>
+      <c r="H42" s="5" t="n">
         <v>73.78</v>
       </c>
-      <c r="I42" s="5" t="n">
+      <c r="I42" s="6" t="n">
         <v>0.1029158875214485</v>
       </c>
-      <c r="J42" s="2" t="n">
+      <c r="J42" s="3" t="n">
         <v>3506</v>
       </c>
-      <c r="K42" s="2" t="n">
+      <c r="K42" s="3" t="n">
         <v>1009</v>
       </c>
     </row>

--- a/summary/no/exposures_meta_analysis_renal_cell_carcinoma_dietary.xlsx
+++ b/summary/no/exposures_meta_analysis_renal_cell_carcinoma_dietary.xlsx
@@ -23,16 +23,13 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -52,7 +49,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -60,22 +57,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -464,57 +452,57 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Exposure</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>number estimates</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Pooled RR</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>lower CI RR</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>upper CI RR</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>lower PI RR</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>upper PI RR</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>I^2 (%)</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eggers p-value</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>total N</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>total Cases</t>
         </is>
@@ -526,26 +514,26 @@
           <t>green_tea</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="4" t="n">
+      <c r="B2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>0.34</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="3" t="n">
         <v>0.21</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" s="3" t="n">
         <v>0.55</v>
       </c>
-      <c r="F2" s="4" t="inlineStr"/>
-      <c r="G2" s="4" t="inlineStr"/>
-      <c r="H2" s="5" t="inlineStr"/>
-      <c r="I2" s="6" t="inlineStr"/>
-      <c r="J2" s="3" t="n">
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr"/>
+      <c r="I2" s="5" t="inlineStr"/>
+      <c r="J2" s="2" t="n">
         <v>549</v>
       </c>
-      <c r="K2" s="3" t="n">
+      <c r="K2" s="2" t="n">
         <v>250</v>
       </c>
     </row>
@@ -555,26 +543,26 @@
           <t>linoleic_acid</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="4" t="n">
+      <c r="B3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="4" t="inlineStr"/>
-      <c r="H3" s="5" t="inlineStr"/>
-      <c r="I3" s="6" t="inlineStr"/>
-      <c r="J3" s="3" t="n">
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" s="5" t="inlineStr"/>
+      <c r="J3" s="2" t="n">
         <v>2301</v>
       </c>
-      <c r="K3" s="3" t="n">
+      <c r="K3" s="2" t="n">
         <v>767</v>
       </c>
     </row>
@@ -584,26 +572,26 @@
           <t>tomato</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="4" t="n">
+      <c r="B4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="3" t="n">
         <v>0.31</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="3" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="6" t="inlineStr"/>
-      <c r="J4" s="3" t="n">
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="2" t="n">
         <v>672</v>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" s="2" t="n">
         <v>335</v>
       </c>
     </row>
@@ -613,26 +601,26 @@
           <t>quercetin</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="4" t="n">
+      <c r="B5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="6" t="inlineStr"/>
-      <c r="J5" s="3" t="n">
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" s="5" t="inlineStr"/>
+      <c r="J5" s="2" t="n">
         <v>27111</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="2" t="n">
         <v>228</v>
       </c>
     </row>
@@ -642,26 +630,26 @@
           <t>eggs</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="4" t="n">
+      <c r="B6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>0.64</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="3" t="n">
         <v>0.48</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="3" t="n">
         <v>0.86</v>
       </c>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="6" t="inlineStr"/>
-      <c r="J6" s="3" t="n">
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="2" t="n">
         <v>1812</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="2" t="n">
         <v>777</v>
       </c>
     </row>
@@ -671,34 +659,34 @@
           <t>vitamin_e</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B7" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="3" t="n">
         <v>0.6704541234521412</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="3" t="n">
         <v>0.4526663314814308</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="3" t="n">
         <v>0.9929251454538985</v>
       </c>
-      <c r="F7" s="4" t="n">
-        <v>0.1198875658484078</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>3.749419120097587</v>
-      </c>
-      <c r="H7" s="5" t="n">
+      <c r="F7" s="3" t="n">
+        <v>0.1198875658458503</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>3.749419120177575</v>
+      </c>
+      <c r="H7" s="4" t="n">
         <v>75.61</v>
       </c>
-      <c r="I7" s="6" t="n">
-        <v>0.5015932102841116</v>
-      </c>
-      <c r="J7" s="3" t="n">
+      <c r="I7" s="5" t="n">
+        <v>0.5015932102841113</v>
+      </c>
+      <c r="J7" s="2" t="n">
         <v>127855</v>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="K7" s="2" t="n">
         <v>2404</v>
       </c>
     </row>
@@ -708,26 +696,26 @@
           <t>anti_inflammatory_diet</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="4" t="n">
+      <c r="B8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>0.68</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="3" t="n">
         <v>0.52</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" s="3" t="n">
         <v>0.89</v>
       </c>
-      <c r="F8" s="4" t="inlineStr"/>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="5" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="3" t="n">
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="2" t="n">
         <v>71421</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="2" t="n">
         <v>431</v>
       </c>
     </row>
@@ -737,28 +725,28 @@
           <t>vitamin_b1</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B9" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" s="3" t="n">
         <v>0.7116279829325146</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="3" t="n">
         <v>0.5506807713861427</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="3" t="n">
         <v>0.9196151607361948</v>
       </c>
-      <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="5" t="n">
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="3" t="n">
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="2" t="n">
         <v>4597</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="2" t="n">
         <v>1909</v>
       </c>
     </row>
@@ -768,34 +756,34 @@
           <t>tea</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" s="3" t="n">
         <v>0.7142658835761514</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="3" t="n">
         <v>0.5123229966574786</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" s="3" t="n">
         <v>0.9958088076649545</v>
       </c>
-      <c r="F10" s="4" t="n">
-        <v>0.1670242223327739</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>3.054501588544217</v>
-      </c>
-      <c r="H10" s="5" t="n">
+      <c r="F10" s="3" t="n">
+        <v>0.1670242223297662</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>3.054501588599221</v>
+      </c>
+      <c r="H10" s="4" t="n">
         <v>77.67</v>
       </c>
-      <c r="I10" s="6" t="n">
-        <v>0.4060945257413281</v>
-      </c>
-      <c r="J10" s="3" t="n">
+      <c r="I10" s="5" t="n">
+        <v>0.4060945257413278</v>
+      </c>
+      <c r="J10" s="2" t="n">
         <v>804643</v>
       </c>
-      <c r="K10" s="3" t="n">
+      <c r="K10" s="2" t="n">
         <v>2861</v>
       </c>
     </row>
@@ -805,34 +793,34 @@
           <t>alcohol</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="C11" s="4" t="n">
+      <c r="C11" s="3" t="n">
         <v>0.7166985207200148</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="3" t="n">
         <v>0.6540967517572572</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="3" t="n">
         <v>0.785291729736156</v>
       </c>
-      <c r="F11" s="4" t="n">
-        <v>0.5315702982473401</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>0.9663007344388015</v>
-      </c>
-      <c r="H11" s="5" t="n">
+      <c r="F11" s="3" t="n">
+        <v>0.5315702982473368</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>0.9663007344388077</v>
+      </c>
+      <c r="H11" s="4" t="n">
         <v>52.61</v>
       </c>
-      <c r="I11" s="6" t="n">
-        <v>0.00190499440164191</v>
-      </c>
-      <c r="J11" s="3" t="n">
+      <c r="I11" s="5" t="n">
+        <v>0.001904994401641916</v>
+      </c>
+      <c r="J11" s="2" t="n">
         <v>3860985</v>
       </c>
-      <c r="K11" s="3" t="n">
+      <c r="K11" s="2" t="n">
         <v>11926</v>
       </c>
     </row>
@@ -842,34 +830,34 @@
           <t>vitamin_c</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C12" s="4" t="n">
+      <c r="C12" s="3" t="n">
         <v>0.7585094662858782</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="3" t="n">
         <v>0.6137301147444475</v>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="E12" s="3" t="n">
         <v>0.9374423653381478</v>
       </c>
-      <c r="F12" s="4" t="n">
-        <v>0.4223806276718763</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>1.36212830975817</v>
-      </c>
-      <c r="H12" s="5" t="n">
+      <c r="F12" s="3" t="n">
+        <v>0.4223806276719194</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>1.362128309758031</v>
+      </c>
+      <c r="H12" s="4" t="n">
         <v>39.11</v>
       </c>
-      <c r="I12" s="6" t="n">
-        <v>0.2965256086013331</v>
-      </c>
-      <c r="J12" s="3" t="n">
+      <c r="I12" s="5" t="n">
+        <v>0.2965256086013334</v>
+      </c>
+      <c r="J12" s="2" t="n">
         <v>128222</v>
       </c>
-      <c r="K12" s="3" t="n">
+      <c r="K12" s="2" t="n">
         <v>2559</v>
       </c>
     </row>
@@ -879,34 +867,34 @@
           <t>lutein</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n">
+      <c r="B13" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C13" s="4" t="n">
+      <c r="C13" s="3" t="n">
         <v>0.7710515858035663</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="3" t="n">
         <v>0.6804506362045877</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" s="3" t="n">
         <v>0.8737159116880344</v>
       </c>
-      <c r="F13" s="4" t="n">
-        <v>0.6293674105587594</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>0.9446319240495346</v>
-      </c>
-      <c r="H13" s="5" t="n">
+      <c r="F13" s="3" t="n">
+        <v>0.6293674105587818</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>0.9446319240495011</v>
+      </c>
+      <c r="H13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="6" t="n">
-        <v>0.5547361243986886</v>
-      </c>
-      <c r="J13" s="3" t="n">
+      <c r="I13" s="5" t="n">
+        <v>0.5547361243986885</v>
+      </c>
+      <c r="J13" s="2" t="n">
         <v>881922</v>
       </c>
-      <c r="K13" s="3" t="n">
+      <c r="K13" s="2" t="n">
         <v>4765</v>
       </c>
     </row>
@@ -916,26 +904,26 @@
           <t>betaine</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="4" t="n">
+      <c r="B14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>0.78</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="3" t="n">
         <v>0.49</v>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="E14" s="3" t="n">
         <v>1.24</v>
       </c>
-      <c r="F14" s="4" t="inlineStr"/>
-      <c r="G14" s="4" t="inlineStr"/>
-      <c r="H14" s="5" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="3" t="n">
+      <c r="F14" s="3" t="inlineStr"/>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="2" t="n">
         <v>77208</v>
       </c>
-      <c r="K14" s="3" t="n">
+      <c r="K14" s="2" t="n">
         <v>225</v>
       </c>
     </row>
@@ -945,26 +933,26 @@
           <t>choline</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="4" t="n">
+      <c r="B15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>0.78</v>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" s="3" t="n">
         <v>0.48</v>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="E15" s="3" t="n">
         <v>1.27</v>
       </c>
-      <c r="F15" s="4" t="inlineStr"/>
-      <c r="G15" s="4" t="inlineStr"/>
-      <c r="H15" s="5" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="3" t="n">
+      <c r="F15" s="3" t="inlineStr"/>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="2" t="n">
         <v>77208</v>
       </c>
-      <c r="K15" s="3" t="n">
+      <c r="K15" s="2" t="n">
         <v>225</v>
       </c>
     </row>
@@ -974,28 +962,28 @@
           <t>vitamin_d</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B16" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C16" s="4" t="n">
+      <c r="C16" s="3" t="n">
         <v>0.7883603473970939</v>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" s="3" t="n">
         <v>0.6542930102200819</v>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="E16" s="3" t="n">
         <v>0.9498986350763723</v>
       </c>
-      <c r="F16" s="4" t="inlineStr"/>
-      <c r="G16" s="4" t="inlineStr"/>
-      <c r="H16" s="5" t="n">
+      <c r="F16" s="3" t="inlineStr"/>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="6" t="inlineStr"/>
-      <c r="J16" s="3" t="n">
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="2" t="n">
         <v>4112</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="2" t="n">
         <v>767</v>
       </c>
     </row>
@@ -1005,28 +993,28 @@
           <t>zeaxanthin</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n">
+      <c r="B17" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C17" s="4" t="n">
+      <c r="C17" s="3" t="n">
         <v>0.7904917964964951</v>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" s="3" t="n">
         <v>0.6716620276620098</v>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E17" s="3" t="n">
         <v>0.9303448082414207</v>
       </c>
-      <c r="F17" s="4" t="inlineStr"/>
-      <c r="G17" s="4" t="inlineStr"/>
-      <c r="H17" s="5" t="n">
+      <c r="F17" s="3" t="inlineStr"/>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I17" s="6" t="inlineStr"/>
-      <c r="J17" s="3" t="n">
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="2" t="n">
         <v>781129</v>
       </c>
-      <c r="K17" s="3" t="n">
+      <c r="K17" s="2" t="n">
         <v>2616</v>
       </c>
     </row>
@@ -1036,26 +1024,26 @@
           <t>vitamin_b3</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" s="4" t="n">
+      <c r="B18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D18" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="E18" s="4" t="n">
+      <c r="E18" s="3" t="n">
         <v>1.07</v>
       </c>
-      <c r="F18" s="4" t="inlineStr"/>
-      <c r="G18" s="4" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="6" t="inlineStr"/>
-      <c r="J18" s="3" t="n">
+      <c r="F18" s="3" t="inlineStr"/>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="4" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="2" t="n">
         <v>2301</v>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" s="2" t="n">
         <v>767</v>
       </c>
     </row>
@@ -1065,28 +1053,28 @@
           <t>total_dietary_fiber_intake</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n">
+      <c r="B19" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C19" s="4" t="n">
+      <c r="C19" s="3" t="n">
         <v>0.8469615338010708</v>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="D19" s="3" t="n">
         <v>0.6424925870144645</v>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E19" s="3" t="n">
         <v>1.116389703847493</v>
       </c>
-      <c r="F19" s="4" t="inlineStr"/>
-      <c r="G19" s="4" t="inlineStr"/>
-      <c r="H19" s="5" t="n">
+      <c r="F19" s="3" t="inlineStr"/>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="4" t="n">
         <v>59.38</v>
       </c>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="3" t="n">
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="2" t="n">
         <v>4410</v>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="K19" s="2" t="n">
         <v>1621</v>
       </c>
     </row>
@@ -1096,26 +1084,26 @@
           <t>vitamin_b6</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" s="4" t="n">
+      <c r="B20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>0.85</v>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D20" s="3" t="n">
         <v>0.64</v>
       </c>
-      <c r="E20" s="4" t="n">
+      <c r="E20" s="3" t="n">
         <v>1.13</v>
       </c>
-      <c r="F20" s="4" t="inlineStr"/>
-      <c r="G20" s="4" t="inlineStr"/>
-      <c r="H20" s="5" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="3" t="n">
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="4" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="2" t="n">
         <v>2301</v>
       </c>
-      <c r="K20" s="3" t="n">
+      <c r="K20" s="2" t="n">
         <v>767</v>
       </c>
     </row>
@@ -1125,26 +1113,26 @@
           <t>vitamin_b2</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" s="4" t="n">
+      <c r="B21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>0.88</v>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="D21" s="3" t="n">
         <v>0.66</v>
       </c>
-      <c r="E21" s="4" t="n">
+      <c r="E21" s="3" t="n">
         <v>1.19</v>
       </c>
-      <c r="F21" s="4" t="inlineStr"/>
-      <c r="G21" s="4" t="inlineStr"/>
-      <c r="H21" s="5" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="3" t="n">
+      <c r="F21" s="3" t="inlineStr"/>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="2" t="n">
         <v>2301</v>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="K21" s="2" t="n">
         <v>767</v>
       </c>
     </row>
@@ -1154,26 +1142,26 @@
           <t>insoluble_dietary_fiber_intake</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" s="4" t="n">
+      <c r="B22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>0.92</v>
       </c>
-      <c r="D22" s="4" t="n">
+      <c r="D22" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="E22" s="4" t="n">
+      <c r="E22" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="F22" s="4" t="inlineStr"/>
-      <c r="G22" s="4" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="6" t="inlineStr"/>
-      <c r="J22" s="3" t="n">
+      <c r="F22" s="3" t="inlineStr"/>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="4" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="2" t="n">
         <v>2301</v>
       </c>
-      <c r="K22" s="3" t="n">
+      <c r="K22" s="2" t="n">
         <v>767</v>
       </c>
     </row>
@@ -1183,34 +1171,34 @@
           <t>beta_carotene</t>
         </is>
       </c>
-      <c r="B23" s="3" t="n">
+      <c r="B23" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C23" s="4" t="n">
+      <c r="C23" s="3" t="n">
         <v>0.9776534669582103</v>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="D23" s="3" t="n">
         <v>0.7008229441190426</v>
       </c>
-      <c r="E23" s="4" t="n">
+      <c r="E23" s="3" t="n">
         <v>1.363697826425325</v>
       </c>
-      <c r="F23" s="4" t="n">
-        <v>0.2848991490980958</v>
-      </c>
-      <c r="G23" s="4" t="n">
-        <v>3.354893492947245</v>
-      </c>
-      <c r="H23" s="5" t="n">
+      <c r="F23" s="3" t="n">
+        <v>0.2848991490981571</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>3.354893492946523</v>
+      </c>
+      <c r="H23" s="4" t="n">
         <v>87.95</v>
       </c>
-      <c r="I23" s="6" t="n">
-        <v>0.7478484537865678</v>
-      </c>
-      <c r="J23" s="3" t="n">
+      <c r="I23" s="5" t="n">
+        <v>0.7478484537865681</v>
+      </c>
+      <c r="J23" s="2" t="n">
         <v>881922</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="2" t="n">
         <v>4765</v>
       </c>
     </row>
@@ -1220,26 +1208,26 @@
           <t>sugar_sweetened_beverage_intake</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" s="4" t="n">
+      <c r="B24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>0.99</v>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D24" s="3" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="E24" s="4" t="n">
+      <c r="E24" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="F24" s="4" t="inlineStr"/>
-      <c r="G24" s="4" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="6" t="inlineStr"/>
-      <c r="J24" s="3" t="n">
+      <c r="F24" s="3" t="inlineStr"/>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="4" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="2" t="n">
         <v>389220</v>
       </c>
-      <c r="K24" s="3" t="n">
+      <c r="K24" s="2" t="n">
         <v>888</v>
       </c>
     </row>
@@ -1249,34 +1237,34 @@
           <t>lycopene</t>
         </is>
       </c>
-      <c r="B25" s="3" t="n">
+      <c r="B25" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C25" s="4" t="n">
+      <c r="C25" s="3" t="n">
         <v>1.017450511698055</v>
       </c>
-      <c r="D25" s="4" t="n">
+      <c r="D25" s="3" t="n">
         <v>0.7301538599450065</v>
       </c>
-      <c r="E25" s="4" t="n">
+      <c r="E25" s="3" t="n">
         <v>1.417790962349503</v>
       </c>
-      <c r="F25" s="4" t="n">
-        <v>0.02227607715280967</v>
-      </c>
-      <c r="G25" s="4" t="n">
-        <v>46.47162678838473</v>
-      </c>
-      <c r="H25" s="5" t="n">
+      <c r="F25" s="3" t="n">
+        <v>0.0222760771545342</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>46.47162678478706</v>
+      </c>
+      <c r="H25" s="4" t="n">
         <v>74.26000000000001</v>
       </c>
-      <c r="I25" s="6" t="n">
-        <v>0.5668230804465443</v>
-      </c>
-      <c r="J25" s="3" t="n">
+      <c r="I25" s="5" t="n">
+        <v>0.5668230804465442</v>
+      </c>
+      <c r="J25" s="2" t="n">
         <v>873444</v>
       </c>
-      <c r="K25" s="3" t="n">
+      <c r="K25" s="2" t="n">
         <v>2860</v>
       </c>
     </row>
@@ -1286,26 +1274,26 @@
           <t>animal_protein_intake</t>
         </is>
       </c>
-      <c r="B26" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="4" t="n">
+      <c r="B26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="D26" s="3" t="n">
         <v>0.85</v>
       </c>
-      <c r="E26" s="4" t="n">
+      <c r="E26" s="3" t="n">
         <v>1.28</v>
       </c>
-      <c r="F26" s="4" t="inlineStr"/>
-      <c r="G26" s="4" t="inlineStr"/>
-      <c r="H26" s="5" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="3" t="n">
+      <c r="F26" s="3" t="inlineStr"/>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="4" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="2" t="n">
         <v>774952</v>
       </c>
-      <c r="K26" s="3" t="n">
+      <c r="K26" s="2" t="n">
         <v>1019</v>
       </c>
     </row>
@@ -1315,26 +1303,26 @@
           <t>monounsaturated_fat_mufa</t>
         </is>
       </c>
-      <c r="B27" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" s="4" t="n">
+      <c r="B27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D27" s="4" t="n">
+      <c r="D27" s="3" t="n">
         <v>0.92</v>
       </c>
-      <c r="E27" s="4" t="n">
+      <c r="E27" s="3" t="n">
         <v>1.32</v>
       </c>
-      <c r="F27" s="4" t="inlineStr"/>
-      <c r="G27" s="4" t="inlineStr"/>
-      <c r="H27" s="5" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="3" t="n">
+      <c r="F27" s="3" t="inlineStr"/>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="4" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="2" t="n">
         <v>774952</v>
       </c>
-      <c r="K27" s="3" t="n">
+      <c r="K27" s="2" t="n">
         <v>1478</v>
       </c>
     </row>
@@ -1344,26 +1332,26 @@
           <t>polyunsaturated_fat_pufa</t>
         </is>
       </c>
-      <c r="B28" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" s="4" t="n">
+      <c r="B28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D28" s="4" t="n">
+      <c r="D28" s="3" t="n">
         <v>0.93</v>
       </c>
-      <c r="E28" s="4" t="n">
+      <c r="E28" s="3" t="n">
         <v>1.31</v>
       </c>
-      <c r="F28" s="4" t="inlineStr"/>
-      <c r="G28" s="4" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="6" t="inlineStr"/>
-      <c r="J28" s="3" t="n">
+      <c r="F28" s="3" t="inlineStr"/>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="4" t="inlineStr"/>
+      <c r="I28" s="5" t="inlineStr"/>
+      <c r="J28" s="2" t="n">
         <v>774952</v>
       </c>
-      <c r="K28" s="3" t="n">
+      <c r="K28" s="2" t="n">
         <v>1478</v>
       </c>
     </row>
@@ -1373,34 +1361,34 @@
           <t>processed_meat_intake</t>
         </is>
       </c>
-      <c r="B29" s="3" t="n">
+      <c r="B29" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="C29" s="4" t="n">
+      <c r="C29" s="3" t="n">
         <v>1.148894298164554</v>
       </c>
-      <c r="D29" s="4" t="n">
+      <c r="D29" s="3" t="n">
         <v>0.9362244820588583</v>
       </c>
-      <c r="E29" s="4" t="n">
+      <c r="E29" s="3" t="n">
         <v>1.410014516884722</v>
       </c>
-      <c r="F29" s="4" t="n">
-        <v>0.6286522321999992</v>
-      </c>
-      <c r="G29" s="4" t="n">
-        <v>2.099663439889119</v>
-      </c>
-      <c r="H29" s="5" t="n">
+      <c r="F29" s="3" t="n">
+        <v>0.6286522321999999</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>2.099663439889117</v>
+      </c>
+      <c r="H29" s="4" t="n">
         <v>77.01000000000001</v>
       </c>
-      <c r="I29" s="6" t="n">
-        <v>0.009615835655054888</v>
-      </c>
-      <c r="J29" s="3" t="n">
+      <c r="I29" s="5" t="n">
+        <v>0.009615835655054882</v>
+      </c>
+      <c r="J29" s="2" t="n">
         <v>1766660</v>
       </c>
-      <c r="K29" s="3" t="n">
+      <c r="K29" s="2" t="n">
         <v>5212</v>
       </c>
     </row>
@@ -1410,28 +1398,28 @@
           <t>folic_acid</t>
         </is>
       </c>
-      <c r="B30" s="3" t="n">
+      <c r="B30" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C30" s="4" t="n">
+      <c r="C30" s="3" t="n">
         <v>1.178214315092722</v>
       </c>
-      <c r="D30" s="4" t="n">
+      <c r="D30" s="3" t="n">
         <v>0.5980385872137474</v>
       </c>
-      <c r="E30" s="4" t="n">
+      <c r="E30" s="3" t="n">
         <v>2.321468593851135</v>
       </c>
-      <c r="F30" s="4" t="inlineStr"/>
-      <c r="G30" s="4" t="inlineStr"/>
-      <c r="H30" s="5" t="n">
+      <c r="F30" s="3" t="inlineStr"/>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="4" t="n">
         <v>85.73999999999999</v>
       </c>
-      <c r="I30" s="6" t="inlineStr"/>
-      <c r="J30" s="3" t="n">
+      <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="2" t="n">
         <v>4597</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="2" t="n">
         <v>1909</v>
       </c>
     </row>
@@ -1441,26 +1429,26 @@
           <t>calcium</t>
         </is>
       </c>
-      <c r="B31" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C31" s="4" t="n">
+      <c r="B31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="D31" s="4" t="n">
+      <c r="D31" s="3" t="n">
         <v>0.92</v>
       </c>
-      <c r="E31" s="4" t="n">
+      <c r="E31" s="3" t="n">
         <v>1.58</v>
       </c>
-      <c r="F31" s="4" t="inlineStr"/>
-      <c r="G31" s="4" t="inlineStr"/>
-      <c r="H31" s="5" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="3" t="n">
+      <c r="F31" s="3" t="inlineStr"/>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="4" t="inlineStr"/>
+      <c r="I31" s="5" t="inlineStr"/>
+      <c r="J31" s="2" t="n">
         <v>1811</v>
       </c>
-      <c r="K31" s="3" t="n">
+      <c r="K31" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1470,28 +1458,28 @@
           <t>vitamin_a</t>
         </is>
       </c>
-      <c r="B32" s="3" t="n">
+      <c r="B32" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C32" s="4" t="n">
+      <c r="C32" s="3" t="n">
         <v>1.227525064963178</v>
       </c>
-      <c r="D32" s="4" t="n">
+      <c r="D32" s="3" t="n">
         <v>0.5259232444453181</v>
       </c>
-      <c r="E32" s="4" t="n">
+      <c r="E32" s="3" t="n">
         <v>2.865377201601115</v>
       </c>
-      <c r="F32" s="4" t="inlineStr"/>
-      <c r="G32" s="4" t="inlineStr"/>
-      <c r="H32" s="5" t="n">
+      <c r="F32" s="3" t="inlineStr"/>
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="4" t="n">
         <v>92.64</v>
       </c>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="3" t="n">
+      <c r="I32" s="5" t="inlineStr"/>
+      <c r="J32" s="2" t="n">
         <v>4597</v>
       </c>
-      <c r="K32" s="3" t="n">
+      <c r="K32" s="2" t="n">
         <v>1909</v>
       </c>
     </row>
@@ -1501,26 +1489,26 @@
           <t>potassium</t>
         </is>
       </c>
-      <c r="B33" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" s="4" t="n">
+      <c r="B33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>1.28</v>
       </c>
-      <c r="D33" s="4" t="n">
+      <c r="D33" s="3" t="n">
         <v>0.87</v>
       </c>
-      <c r="E33" s="4" t="n">
+      <c r="E33" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="F33" s="4" t="inlineStr"/>
-      <c r="G33" s="4" t="inlineStr"/>
-      <c r="H33" s="5" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="3" t="n">
+      <c r="F33" s="3" t="inlineStr"/>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="4" t="inlineStr"/>
+      <c r="I33" s="5" t="inlineStr"/>
+      <c r="J33" s="2" t="n">
         <v>120852</v>
       </c>
-      <c r="K33" s="3" t="n">
+      <c r="K33" s="2" t="n">
         <v>485</v>
       </c>
     </row>
@@ -1530,28 +1518,28 @@
           <t>dietary_protein_intake</t>
         </is>
       </c>
-      <c r="B34" s="3" t="n">
+      <c r="B34" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C34" s="4" t="n">
+      <c r="C34" s="3" t="n">
         <v>1.303822063731362</v>
       </c>
-      <c r="D34" s="4" t="n">
+      <c r="D34" s="3" t="n">
         <v>0.7543491156730364</v>
       </c>
-      <c r="E34" s="4" t="n">
+      <c r="E34" s="3" t="n">
         <v>2.253760151959979</v>
       </c>
-      <c r="F34" s="4" t="inlineStr"/>
-      <c r="G34" s="4" t="inlineStr"/>
-      <c r="H34" s="5" t="n">
+      <c r="F34" s="3" t="inlineStr"/>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="4" t="n">
         <v>66.34</v>
       </c>
-      <c r="I34" s="6" t="inlineStr"/>
-      <c r="J34" s="3" t="n">
+      <c r="I34" s="5" t="inlineStr"/>
+      <c r="J34" s="2" t="n">
         <v>776349</v>
       </c>
-      <c r="K34" s="3" t="n">
+      <c r="K34" s="2" t="n">
         <v>2168</v>
       </c>
     </row>
@@ -1561,26 +1549,26 @@
           <t>yogurt</t>
         </is>
       </c>
-      <c r="B35" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" s="4" t="n">
+      <c r="B35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>1.31</v>
       </c>
-      <c r="D35" s="4" t="n">
+      <c r="D35" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="E35" s="4" t="n">
+      <c r="E35" s="3" t="n">
         <v>1.67</v>
       </c>
-      <c r="F35" s="4" t="inlineStr"/>
-      <c r="G35" s="4" t="inlineStr"/>
-      <c r="H35" s="5" t="inlineStr"/>
-      <c r="I35" s="6" t="inlineStr"/>
-      <c r="J35" s="3" t="n">
+      <c r="F35" s="3" t="inlineStr"/>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="4" t="inlineStr"/>
+      <c r="I35" s="5" t="inlineStr"/>
+      <c r="J35" s="2" t="n">
         <v>1812</v>
       </c>
-      <c r="K35" s="3" t="n">
+      <c r="K35" s="2" t="n">
         <v>777</v>
       </c>
     </row>
@@ -1590,28 +1578,28 @@
           <t>ultra_processed_food_intake</t>
         </is>
       </c>
-      <c r="B36" s="3" t="n">
+      <c r="B36" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C36" s="4" t="n">
+      <c r="C36" s="3" t="n">
         <v>1.37520113442151</v>
       </c>
-      <c r="D36" s="4" t="n">
+      <c r="D36" s="3" t="n">
         <v>1.02009932499359</v>
       </c>
-      <c r="E36" s="4" t="n">
+      <c r="E36" s="3" t="n">
         <v>1.854101106672441</v>
       </c>
-      <c r="F36" s="4" t="inlineStr"/>
-      <c r="G36" s="4" t="inlineStr"/>
-      <c r="H36" s="5" t="n">
+      <c r="F36" s="3" t="inlineStr"/>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I36" s="6" t="inlineStr"/>
-      <c r="J36" s="3" t="n">
+      <c r="I36" s="5" t="inlineStr"/>
+      <c r="J36" s="2" t="n">
         <v>647537</v>
       </c>
-      <c r="K36" s="3" t="n">
+      <c r="K36" s="2" t="n">
         <v>594</v>
       </c>
     </row>
@@ -1621,34 +1609,34 @@
           <t>red_meat</t>
         </is>
       </c>
-      <c r="B37" s="3" t="n">
+      <c r="B37" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="C37" s="4" t="n">
+      <c r="C37" s="3" t="n">
         <v>1.428035894777088</v>
       </c>
-      <c r="D37" s="4" t="n">
+      <c r="D37" s="3" t="n">
         <v>1.125806874101985</v>
       </c>
-      <c r="E37" s="4" t="n">
+      <c r="E37" s="3" t="n">
         <v>1.811399951166991</v>
       </c>
-      <c r="F37" s="4" t="n">
-        <v>0.6711000405372333</v>
-      </c>
-      <c r="G37" s="4" t="n">
-        <v>3.038722088497114</v>
-      </c>
-      <c r="H37" s="5" t="n">
+      <c r="F37" s="3" t="n">
+        <v>0.6711000405372343</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>3.03872208849711</v>
+      </c>
+      <c r="H37" s="4" t="n">
         <v>81.58</v>
       </c>
-      <c r="I37" s="6" t="n">
-        <v>0.01776300266501834</v>
-      </c>
-      <c r="J37" s="3" t="n">
+      <c r="I37" s="5" t="n">
+        <v>0.01776300266501832</v>
+      </c>
+      <c r="J37" s="2" t="n">
         <v>1768446</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="2" t="n">
         <v>5800</v>
       </c>
     </row>
@@ -1658,26 +1646,26 @@
           <t>docosahexaenoic_acid</t>
         </is>
       </c>
-      <c r="B38" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" s="4" t="n">
+      <c r="B38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>1.56</v>
       </c>
-      <c r="D38" s="4" t="n">
+      <c r="D38" s="3" t="n">
         <v>1.07</v>
       </c>
-      <c r="E38" s="4" t="n">
+      <c r="E38" s="3" t="n">
         <v>2.27</v>
       </c>
-      <c r="F38" s="4" t="inlineStr"/>
-      <c r="G38" s="4" t="inlineStr"/>
-      <c r="H38" s="5" t="inlineStr"/>
-      <c r="I38" s="6" t="inlineStr"/>
-      <c r="J38" s="3" t="n">
+      <c r="F38" s="3" t="inlineStr"/>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="4" t="inlineStr"/>
+      <c r="I38" s="5" t="inlineStr"/>
+      <c r="J38" s="2" t="n">
         <v>84063</v>
       </c>
-      <c r="K38" s="3" t="n">
+      <c r="K38" s="2" t="n">
         <v>262</v>
       </c>
     </row>
@@ -1687,26 +1675,26 @@
           <t>omega_3_fatty_acids</t>
         </is>
       </c>
-      <c r="B39" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C39" s="4" t="n">
+      <c r="B39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>1.56</v>
       </c>
-      <c r="D39" s="4" t="n">
+      <c r="D39" s="3" t="n">
         <v>1.07</v>
       </c>
-      <c r="E39" s="4" t="n">
+      <c r="E39" s="3" t="n">
         <v>2.28</v>
       </c>
-      <c r="F39" s="4" t="inlineStr"/>
-      <c r="G39" s="4" t="inlineStr"/>
-      <c r="H39" s="5" t="inlineStr"/>
-      <c r="I39" s="6" t="inlineStr"/>
-      <c r="J39" s="3" t="n">
+      <c r="F39" s="3" t="inlineStr"/>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="4" t="inlineStr"/>
+      <c r="I39" s="5" t="inlineStr"/>
+      <c r="J39" s="2" t="n">
         <v>84063</v>
       </c>
-      <c r="K39" s="3" t="n">
+      <c r="K39" s="2" t="n">
         <v>262</v>
       </c>
     </row>
@@ -1716,26 +1704,26 @@
           <t>oleic_acid</t>
         </is>
       </c>
-      <c r="B40" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" s="4" t="n">
+      <c r="B40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="D40" s="4" t="n">
+      <c r="D40" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="E40" s="4" t="n">
+      <c r="E40" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="F40" s="4" t="inlineStr"/>
-      <c r="G40" s="4" t="inlineStr"/>
-      <c r="H40" s="5" t="inlineStr"/>
-      <c r="I40" s="6" t="inlineStr"/>
-      <c r="J40" s="3" t="n">
+      <c r="F40" s="3" t="inlineStr"/>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="4" t="inlineStr"/>
+      <c r="I40" s="5" t="inlineStr"/>
+      <c r="J40" s="2" t="n">
         <v>2143</v>
       </c>
-      <c r="K40" s="3" t="n">
+      <c r="K40" s="2" t="n">
         <v>323</v>
       </c>
     </row>
@@ -1745,26 +1733,26 @@
           <t>selenium</t>
         </is>
       </c>
-      <c r="B41" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C41" s="4" t="n">
+      <c r="B41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D41" s="4" t="n">
+      <c r="D41" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="E41" s="4" t="n">
+      <c r="E41" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="F41" s="4" t="inlineStr"/>
-      <c r="G41" s="4" t="inlineStr"/>
-      <c r="H41" s="5" t="inlineStr"/>
-      <c r="I41" s="6" t="inlineStr"/>
-      <c r="J41" s="3" t="n">
+      <c r="F41" s="3" t="inlineStr"/>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="4" t="inlineStr"/>
+      <c r="I41" s="5" t="inlineStr"/>
+      <c r="J41" s="2" t="n">
         <v>2296</v>
       </c>
-      <c r="K41" s="3" t="n">
+      <c r="K41" s="2" t="n">
         <v>1142</v>
       </c>
     </row>
@@ -1774,34 +1762,34 @@
           <t>dairy</t>
         </is>
       </c>
-      <c r="B42" s="3" t="n">
+      <c r="B42" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C42" s="4" t="n">
+      <c r="C42" s="3" t="n">
         <v>2.715293362405407</v>
       </c>
-      <c r="D42" s="4" t="n">
+      <c r="D42" s="3" t="n">
         <v>1.217987613870554</v>
       </c>
-      <c r="E42" s="4" t="n">
+      <c r="E42" s="3" t="n">
         <v>6.052673044477135</v>
       </c>
-      <c r="F42" s="4" t="n">
-        <v>0.0003047814843291999</v>
-      </c>
-      <c r="G42" s="4" t="n">
-        <v>24190.50507661207</v>
-      </c>
-      <c r="H42" s="5" t="n">
+      <c r="F42" s="3" t="n">
+        <v>0.0003047814843853535</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>24190.50507215516</v>
+      </c>
+      <c r="H42" s="4" t="n">
         <v>73.78</v>
       </c>
-      <c r="I42" s="6" t="n">
+      <c r="I42" s="5" t="n">
         <v>0.1029158875214485</v>
       </c>
-      <c r="J42" s="3" t="n">
+      <c r="J42" s="2" t="n">
         <v>3506</v>
       </c>
-      <c r="K42" s="3" t="n">
+      <c r="K42" s="2" t="n">
         <v>1009</v>
       </c>
     </row>
